--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-02.xlsx
@@ -1441,7 +1441,7 @@
     <t>Universitario de Deportes</t>
   </si>
   <si>
-    <t>2026-08-01 00:30:37</t>
+    <t>2026-08-01 02:51:55</t>
   </si>
 </sst>
 </file>
@@ -2035,58 +2035,58 @@
         <v>328</v>
       </c>
       <c r="F2">
-        <v>2.22</v>
+        <v>2.44</v>
       </c>
       <c r="G2">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="H2">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="I2">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="J2">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L2">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M2">
         <v>1.06</v>
       </c>
       <c r="N2">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="O2">
         <v>1.3</v>
       </c>
       <c r="P2">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="Q2">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="R2">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S2">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="T2">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U2">
         <v>2.18</v>
       </c>
       <c r="V2">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="W2">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="X2">
         <v>17.5</v>
@@ -2095,10 +2095,10 @@
         <v>14.5</v>
       </c>
       <c r="Z2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AA2">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB2">
         <v>12.5</v>
@@ -2110,10 +2110,10 @@
         <v>15.5</v>
       </c>
       <c r="AE2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AF2">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AG2">
         <v>13</v>
@@ -2122,13 +2122,13 @@
         <v>18</v>
       </c>
       <c r="AI2">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ2">
         <v>36</v>
       </c>
       <c r="AK2">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AL2">
         <v>42</v>
@@ -2137,10 +2137,10 @@
         <v>100</v>
       </c>
       <c r="AN2">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AO2">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AP2">
         <v>11.5</v>
@@ -2152,10 +2152,10 @@
         <v>18.5</v>
       </c>
       <c r="AS2">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="AT2">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU2">
         <v>7</v>
@@ -2164,37 +2164,37 @@
         <v>11</v>
       </c>
       <c r="AW2">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="AX2">
         <v>11.5</v>
       </c>
       <c r="AY2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ2">
         <v>14.5</v>
       </c>
       <c r="BA2">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BB2">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="BC2">
         <v>18</v>
       </c>
       <c r="BD2">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="BE2">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BF2">
         <v>13</v>
       </c>
       <c r="BG2">
-        <v>5.9</v>
+        <v>5.3</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -2277,46 +2277,46 @@
         <v>329</v>
       </c>
       <c r="F3">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="G3">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H3">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="I3">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J3">
         <v>3.2</v>
       </c>
       <c r="K3">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="L3">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="M3">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="O3">
         <v>1.49</v>
       </c>
       <c r="P3">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="Q3">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R3">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="S3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T3">
         <v>1.11</v>
@@ -2325,10 +2325,10 @@
         <v>1.74</v>
       </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -2531,34 +2531,34 @@
         <v>3.75</v>
       </c>
       <c r="J4">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="K4">
         <v>4.1</v>
       </c>
       <c r="L4">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M4">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N4">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="O4">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P4">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="Q4">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="R4">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S4">
-        <v>2.52</v>
+        <v>2.78</v>
       </c>
       <c r="T4">
         <v>1.46</v>
@@ -2764,16 +2764,16 @@
         <v>3.3</v>
       </c>
       <c r="G5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H5">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I5">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="J5">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K5">
         <v>3.75</v>
@@ -2785,31 +2785,31 @@
         <v>1.05</v>
       </c>
       <c r="N5">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O5">
         <v>1.23</v>
       </c>
       <c r="P5">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q5">
         <v>1.71</v>
       </c>
       <c r="R5">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S5">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T5">
         <v>1.59</v>
       </c>
       <c r="U5">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="V5">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="W5">
         <v>1.42</v>
@@ -2818,10 +2818,10 @@
         <v>21</v>
       </c>
       <c r="Y5">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z5">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AA5">
         <v>32</v>
@@ -2833,16 +2833,16 @@
         <v>8.4</v>
       </c>
       <c r="AD5">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AE5">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AF5">
         <v>26</v>
       </c>
       <c r="AG5">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AH5">
         <v>14.5</v>
@@ -2854,7 +2854,7 @@
         <v>60</v>
       </c>
       <c r="AK5">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AL5">
         <v>38</v>
@@ -2899,10 +2899,10 @@
         <v>12.5</v>
       </c>
       <c r="AZ5">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB5">
         <v>48</v>
@@ -2917,70 +2917,70 @@
         <v>30</v>
       </c>
       <c r="BF5">
+        <v>21</v>
+      </c>
+      <c r="BG5">
+        <v>12</v>
+      </c>
+      <c r="BH5">
+        <v>4</v>
+      </c>
+      <c r="BI5">
+        <v>3.25</v>
+      </c>
+      <c r="BJ5">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BK5">
+        <v>7.8</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
         <v>22</v>
       </c>
-      <c r="BG5">
-        <v>12.5</v>
-      </c>
-      <c r="BH5">
-        <v>1000</v>
-      </c>
-      <c r="BI5">
-        <v>1.01</v>
-      </c>
-      <c r="BJ5">
-        <v>1000</v>
-      </c>
-      <c r="BK5">
-        <v>1.01</v>
-      </c>
-      <c r="BL5">
-        <v>1000</v>
-      </c>
-      <c r="BM5">
-        <v>1.01</v>
-      </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BV5">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="CB5" t="s">
         <v>475</v>
@@ -3012,10 +3012,10 @@
         <v>3.45</v>
       </c>
       <c r="I6">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J6">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>4.2</v>
@@ -3027,13 +3027,13 @@
         <v>1.03</v>
       </c>
       <c r="N6">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O6">
         <v>1.18</v>
       </c>
       <c r="P6">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q6">
         <v>1.57</v>
@@ -3051,10 +3051,10 @@
         <v>2.74</v>
       </c>
       <c r="V6">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="X6">
         <v>27</v>
@@ -3066,7 +3066,7 @@
         <v>34</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB6">
         <v>15.5</v>
@@ -3090,7 +3090,7 @@
         <v>15</v>
       </c>
       <c r="AI6">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ6">
         <v>27</v>
@@ -3099,10 +3099,10 @@
         <v>19.5</v>
       </c>
       <c r="AL6">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AM6">
-        <v>320</v>
+        <v>55</v>
       </c>
       <c r="AN6">
         <v>9.800000000000001</v>
@@ -3111,19 +3111,19 @@
         <v>24</v>
       </c>
       <c r="AP6">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AQ6">
         <v>17.5</v>
       </c>
       <c r="AR6">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="AS6">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="AT6">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU6">
         <v>8.800000000000001</v>
@@ -3132,7 +3132,7 @@
         <v>13</v>
       </c>
       <c r="AW6">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="AX6">
         <v>14</v>
@@ -3144,10 +3144,10 @@
         <v>13</v>
       </c>
       <c r="BA6">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BB6">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BC6">
         <v>16.5</v>
@@ -3165,64 +3165,64 @@
         <v>20</v>
       </c>
       <c r="BH6">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BI6">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="CB6" t="s">
         <v>475</v>
@@ -3245,22 +3245,22 @@
         <v>333</v>
       </c>
       <c r="F7">
+        <v>1.57</v>
+      </c>
+      <c r="G7">
         <v>1.58</v>
       </c>
-      <c r="G7">
-        <v>1.6</v>
-      </c>
       <c r="H7">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J7">
         <v>5</v>
       </c>
       <c r="K7">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L7">
         <v>1.25</v>
@@ -3272,10 +3272,10 @@
         <v>6.8</v>
       </c>
       <c r="O7">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P7">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="Q7">
         <v>1.48</v>
@@ -3290,10 +3290,10 @@
         <v>1.6</v>
       </c>
       <c r="U7">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V7">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W7">
         <v>2.68</v>
@@ -3311,7 +3311,7 @@
         <v>150</v>
       </c>
       <c r="AB7">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC7">
         <v>12</v>
@@ -3323,7 +3323,7 @@
         <v>60</v>
       </c>
       <c r="AF7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG7">
         <v>10.5</v>
@@ -3338,7 +3338,7 @@
         <v>16.5</v>
       </c>
       <c r="AK7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AL7">
         <v>24</v>
@@ -3347,13 +3347,13 @@
         <v>65</v>
       </c>
       <c r="AN7">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AO7">
         <v>46</v>
       </c>
       <c r="AP7">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AQ7">
         <v>29</v>
@@ -3362,10 +3362,10 @@
         <v>48</v>
       </c>
       <c r="AS7">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT7">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU7">
         <v>11</v>
@@ -3386,7 +3386,7 @@
         <v>16</v>
       </c>
       <c r="BA7">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="BB7">
         <v>15</v>
@@ -3404,7 +3404,7 @@
         <v>5.1</v>
       </c>
       <c r="BG7">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -3508,37 +3508,37 @@
         <v>1.29</v>
       </c>
       <c r="M8">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="O8">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P8">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="Q8">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="R8">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="S8">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="T8">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U8">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="V8">
         <v>1.38</v>
       </c>
       <c r="W8">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X8">
         <v>26</v>
@@ -3553,7 +3553,7 @@
         <v>65</v>
       </c>
       <c r="AB8">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AC8">
         <v>9.6</v>
@@ -3571,34 +3571,34 @@
         <v>11</v>
       </c>
       <c r="AH8">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AI8">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ8">
         <v>26</v>
       </c>
       <c r="AK8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL8">
         <v>26</v>
       </c>
       <c r="AM8">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN8">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AO8">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AP8">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AQ8">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR8">
         <v>27</v>
@@ -3610,7 +3610,7 @@
         <v>13.5</v>
       </c>
       <c r="AU8">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV8">
         <v>14</v>
@@ -3640,19 +3640,19 @@
         <v>23</v>
       </c>
       <c r="BE8">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF8">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BG8">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BH8">
         <v>4.5</v>
       </c>
       <c r="BI8">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="BJ8">
         <v>8.6</v>
@@ -3661,7 +3661,7 @@
         <v>6.4</v>
       </c>
       <c r="BL8">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BM8">
         <v>50</v>
@@ -3673,13 +3673,13 @@
         <v>4.8</v>
       </c>
       <c r="BP8">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ8">
         <v>10</v>
       </c>
       <c r="BR8">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BS8">
         <v>13.5</v>
@@ -3691,19 +3691,19 @@
         <v>4.8</v>
       </c>
       <c r="BV8">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BW8">
         <v>15</v>
       </c>
       <c r="BX8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BY8">
         <v>17.5</v>
       </c>
       <c r="BZ8">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="CA8">
         <v>11</v>
@@ -3729,7 +3729,7 @@
         <v>335</v>
       </c>
       <c r="F9">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G9">
         <v>3.15</v>
@@ -3747,28 +3747,28 @@
         <v>3.7</v>
       </c>
       <c r="L9">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M9">
         <v>1.06</v>
       </c>
       <c r="N9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O9">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P9">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q9">
         <v>1.89</v>
       </c>
       <c r="R9">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S9">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T9">
         <v>1.72</v>
@@ -3783,7 +3783,7 @@
         <v>1.46</v>
       </c>
       <c r="X9">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y9">
         <v>11.5</v>
@@ -3792,7 +3792,7 @@
         <v>16.5</v>
       </c>
       <c r="AA9">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AB9">
         <v>13.5</v>
@@ -3813,7 +3813,7 @@
         <v>14.5</v>
       </c>
       <c r="AH9">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI9">
         <v>44</v>
@@ -3834,7 +3834,7 @@
         <v>50</v>
       </c>
       <c r="AO9">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP9">
         <v>14</v>
@@ -3846,7 +3846,7 @@
         <v>14</v>
       </c>
       <c r="AS9">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AT9">
         <v>11.5</v>
@@ -3858,7 +3858,7 @@
         <v>10</v>
       </c>
       <c r="AW9">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AX9">
         <v>17.5</v>
@@ -3870,19 +3870,19 @@
         <v>14.5</v>
       </c>
       <c r="BA9">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB9">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC9">
-        <v>7.2</v>
+        <v>29</v>
       </c>
       <c r="BD9">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BE9">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF9">
         <v>21</v>
@@ -3971,13 +3971,13 @@
         <v>336</v>
       </c>
       <c r="F10">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G10">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H10">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="I10">
         <v>990</v>
@@ -3989,10 +3989,10 @@
         <v>950</v>
       </c>
       <c r="L10">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N10">
         <v>4.9</v>
@@ -4001,13 +4001,13 @@
         <v>1.21</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="Q10">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R10">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S10">
         <v>2.42</v>
@@ -4216,46 +4216,46 @@
         <v>2.74</v>
       </c>
       <c r="G11">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="H11">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="I11">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J11">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K11">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L11">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="M11">
         <v>1.07</v>
       </c>
       <c r="N11">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O11">
         <v>1.34</v>
       </c>
       <c r="P11">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q11">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="R11">
         <v>1.37</v>
       </c>
       <c r="S11">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T11">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U11">
         <v>2.14</v>
@@ -4276,7 +4276,7 @@
         <v>18</v>
       </c>
       <c r="AA11">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AB11">
         <v>11.5</v>
@@ -4285,10 +4285,10 @@
         <v>8</v>
       </c>
       <c r="AD11">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE11">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AF11">
         <v>19</v>
@@ -4297,19 +4297,19 @@
         <v>13.5</v>
       </c>
       <c r="AH11">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AI11">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AJ11">
         <v>46</v>
       </c>
       <c r="AK11">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AL11">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM11">
         <v>110</v>
@@ -4330,7 +4330,7 @@
         <v>15</v>
       </c>
       <c r="AS11">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT11">
         <v>9.800000000000001</v>
@@ -4342,7 +4342,7 @@
         <v>11</v>
       </c>
       <c r="AW11">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX11">
         <v>16</v>
@@ -4354,19 +4354,19 @@
         <v>15.5</v>
       </c>
       <c r="BA11">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB11">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BC11">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="BD11">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BE11">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF11">
         <v>20</v>
@@ -4455,58 +4455,58 @@
         <v>338</v>
       </c>
       <c r="F12">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G12">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H12">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I12">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K12">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L12">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M12">
         <v>1.08</v>
       </c>
       <c r="N12">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="O12">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="P12">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="Q12">
         <v>2.06</v>
       </c>
       <c r="R12">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S12">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="T12">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="U12">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="V12">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W12">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X12">
         <v>15.5</v>
@@ -4542,16 +4542,16 @@
         <v>19.5</v>
       </c>
       <c r="AI12">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ12">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AK12">
         <v>26</v>
       </c>
       <c r="AL12">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM12">
         <v>130</v>
@@ -4569,10 +4569,10 @@
         <v>11.5</v>
       </c>
       <c r="AR12">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS12">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT12">
         <v>7.6</v>
@@ -4584,7 +4584,7 @@
         <v>13.5</v>
       </c>
       <c r="AW12">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX12">
         <v>11.5</v>
@@ -4596,19 +4596,19 @@
         <v>15.5</v>
       </c>
       <c r="BA12">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BB12">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BC12">
         <v>20</v>
       </c>
       <c r="BD12">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE12">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BF12">
         <v>14</v>
@@ -4617,16 +4617,16 @@
         <v>38</v>
       </c>
       <c r="BH12">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI12">
         <v>2.64</v>
       </c>
       <c r="BJ12">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK12">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL12">
         <v>1000</v>
@@ -4641,19 +4641,19 @@
         <v>3.8</v>
       </c>
       <c r="BP12">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ12">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BR12">
         <v>32</v>
       </c>
       <c r="BS12">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT12">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BU12">
         <v>5.3</v>
@@ -4662,7 +4662,7 @@
         <v>34</v>
       </c>
       <c r="BW12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BX12">
         <v>46</v>
@@ -4697,13 +4697,13 @@
         <v>339</v>
       </c>
       <c r="F13">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="G13">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H13">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>13</v>
@@ -4712,37 +4712,37 @@
         <v>4.7</v>
       </c>
       <c r="K13">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L13">
-        <v>1.13</v>
+        <v>1.4</v>
       </c>
       <c r="M13">
         <v>1.06</v>
       </c>
       <c r="N13">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="O13">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P13">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q13">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="R13">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S13">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="T13">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="U13">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V13">
         <v>1.08</v>
@@ -4757,13 +4757,13 @@
         <v>44</v>
       </c>
       <c r="Z13">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AB13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AC13">
         <v>12</v>
@@ -4772,19 +4772,19 @@
         <v>65</v>
       </c>
       <c r="AE13">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AF13">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AG13">
         <v>11</v>
       </c>
       <c r="AH13">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AI13">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AJ13">
         <v>11.5</v>
@@ -4796,25 +4796,25 @@
         <v>70</v>
       </c>
       <c r="AM13">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN13">
         <v>7.8</v>
       </c>
       <c r="AO13">
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="AP13">
         <v>13</v>
       </c>
       <c r="AQ13">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR13">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS13">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AT13">
         <v>5.9</v>
@@ -4823,10 +4823,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV13">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="AW13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AX13">
         <v>6.2</v>
@@ -4835,10 +4835,10 @@
         <v>9</v>
       </c>
       <c r="AZ13">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BB13">
         <v>9.4</v>
@@ -4850,13 +4850,13 @@
         <v>40</v>
       </c>
       <c r="BE13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BF13">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BG13">
-        <v>8.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4942,13 +4942,13 @@
         <v>1.82</v>
       </c>
       <c r="G14">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="H14">
         <v>4.5</v>
       </c>
       <c r="I14">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J14">
         <v>4.1</v>
@@ -4969,7 +4969,7 @@
         <v>1.25</v>
       </c>
       <c r="P14">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="Q14">
         <v>1.75</v>
@@ -4978,7 +4978,7 @@
         <v>1.49</v>
       </c>
       <c r="S14">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T14">
         <v>1.71</v>
@@ -4987,16 +4987,16 @@
         <v>2.32</v>
       </c>
       <c r="V14">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W14">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X14">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="Y14">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="Z14">
         <v>70</v>
@@ -5014,7 +5014,7 @@
         <v>18</v>
       </c>
       <c r="AE14">
-        <v>290</v>
+        <v>60</v>
       </c>
       <c r="AF14">
         <v>12.5</v>
@@ -5023,10 +5023,10 @@
         <v>10</v>
       </c>
       <c r="AH14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI14">
-        <v>400</v>
+        <v>55</v>
       </c>
       <c r="AJ14">
         <v>21</v>
@@ -5035,7 +5035,7 @@
         <v>18.5</v>
       </c>
       <c r="AL14">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AM14">
         <v>1000</v>
@@ -5044,16 +5044,16 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AO14">
-        <v>220</v>
+        <v>55</v>
       </c>
       <c r="AP14">
         <v>17.5</v>
       </c>
       <c r="AQ14">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AR14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AS14">
         <v>38</v>
@@ -5068,7 +5068,7 @@
         <v>15.5</v>
       </c>
       <c r="AW14">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AX14">
         <v>11</v>
@@ -5080,7 +5080,7 @@
         <v>16</v>
       </c>
       <c r="BA14">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BB14">
         <v>17</v>
@@ -5089,7 +5089,7 @@
         <v>16</v>
       </c>
       <c r="BD14">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BE14">
         <v>36</v>
@@ -5098,7 +5098,7 @@
         <v>8.6</v>
       </c>
       <c r="BG14">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -5205,13 +5205,13 @@
         <v>1.03</v>
       </c>
       <c r="N15">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O15">
         <v>1.18</v>
       </c>
       <c r="P15">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="Q15">
         <v>1.55</v>
@@ -5235,16 +5235,16 @@
         <v>1.78</v>
       </c>
       <c r="X15">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="Y15">
         <v>21</v>
       </c>
       <c r="Z15">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AA15">
-        <v>230</v>
+        <v>60</v>
       </c>
       <c r="AB15">
         <v>16.5</v>
@@ -5280,7 +5280,7 @@
         <v>28</v>
       </c>
       <c r="AM15">
-        <v>190</v>
+        <v>60</v>
       </c>
       <c r="AN15">
         <v>10.5</v>
@@ -5295,10 +5295,10 @@
         <v>17.5</v>
       </c>
       <c r="AR15">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="AS15">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AT15">
         <v>14</v>
@@ -5310,10 +5310,10 @@
         <v>12.5</v>
       </c>
       <c r="AW15">
-        <v>19.5</v>
+        <v>26</v>
       </c>
       <c r="AX15">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AY15">
         <v>10</v>
@@ -5325,13 +5325,13 @@
         <v>23</v>
       </c>
       <c r="BB15">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BC15">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BD15">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BE15">
         <v>27</v>
@@ -5423,13 +5423,13 @@
         <v>342</v>
       </c>
       <c r="F16">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G16">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="H16">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I16">
         <v>3.15</v>
@@ -5447,22 +5447,22 @@
         <v>1.03</v>
       </c>
       <c r="N16">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O16">
         <v>1.17</v>
       </c>
       <c r="P16">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="Q16">
         <v>1.52</v>
       </c>
       <c r="R16">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="S16">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T16">
         <v>1.49</v>
@@ -5474,7 +5474,7 @@
         <v>1.46</v>
       </c>
       <c r="W16">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="X16">
         <v>28</v>
@@ -5489,7 +5489,7 @@
         <v>55</v>
       </c>
       <c r="AB16">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC16">
         <v>10.5</v>
@@ -5498,13 +5498,13 @@
         <v>14</v>
       </c>
       <c r="AE16">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="AF16">
         <v>19.5</v>
       </c>
       <c r="AG16">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH16">
         <v>14.5</v>
@@ -5522,13 +5522,13 @@
         <v>25</v>
       </c>
       <c r="AM16">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN16">
         <v>10.5</v>
       </c>
       <c r="AO16">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AP16">
         <v>25</v>
@@ -5537,10 +5537,10 @@
         <v>18.5</v>
       </c>
       <c r="AR16">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS16">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT16">
         <v>15.5</v>
@@ -5576,13 +5576,13 @@
         <v>22</v>
       </c>
       <c r="BE16">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF16">
         <v>9</v>
       </c>
       <c r="BG16">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -5591,58 +5591,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BL16">
         <v>1000</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB16" t="s">
         <v>475</v>
@@ -5665,10 +5665,10 @@
         <v>343</v>
       </c>
       <c r="F17">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G17">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H17">
         <v>9.4</v>
@@ -5677,34 +5677,34 @@
         <v>10.5</v>
       </c>
       <c r="J17">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="K17">
         <v>6.2</v>
       </c>
       <c r="L17">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N17">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P17">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Q17">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R17">
         <v>1.65</v>
       </c>
       <c r="S17">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="T17">
         <v>1.9</v>
@@ -5716,7 +5716,7 @@
         <v>1.1</v>
       </c>
       <c r="W17">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X17">
         <v>28</v>
@@ -6403,7 +6403,7 @@
         <v>990</v>
       </c>
       <c r="J20">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K20">
         <v>950</v>
@@ -6442,7 +6442,7 @@
         <v>1.02</v>
       </c>
       <c r="W20">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -6633,10 +6633,10 @@
         <v>347</v>
       </c>
       <c r="F21">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="G21">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="H21">
         <v>4.3</v>
@@ -6663,10 +6663,10 @@
         <v>1.21</v>
       </c>
       <c r="P21">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q21">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R21">
         <v>1.54</v>
@@ -6684,7 +6684,7 @@
         <v>1.25</v>
       </c>
       <c r="W21">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X21">
         <v>24</v>
@@ -6908,7 +6908,7 @@
         <v>1.97</v>
       </c>
       <c r="Q22">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="R22">
         <v>1.37</v>
@@ -6917,10 +6917,10 @@
         <v>3.1</v>
       </c>
       <c r="T22">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="U22">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="V22">
         <v>1.12</v>
@@ -7135,7 +7135,7 @@
         <v>3.95</v>
       </c>
       <c r="L23">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="M23">
         <v>1.06</v>
@@ -7147,22 +7147,22 @@
         <v>1.3</v>
       </c>
       <c r="P23">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q23">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="R23">
         <v>1.41</v>
       </c>
       <c r="S23">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T23">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U23">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V23">
         <v>1.3</v>
@@ -7365,7 +7365,7 @@
         <v>3.5</v>
       </c>
       <c r="H24">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="I24">
         <v>2.7</v>
@@ -7389,7 +7389,7 @@
         <v>1.5</v>
       </c>
       <c r="P24">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Q24">
         <v>2.44</v>
@@ -7470,7 +7470,7 @@
         <v>8.4</v>
       </c>
       <c r="AQ24">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR24">
         <v>13</v>
@@ -7488,7 +7488,7 @@
         <v>11</v>
       </c>
       <c r="AW24">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX24">
         <v>18</v>
@@ -7497,37 +7497,37 @@
         <v>13</v>
       </c>
       <c r="AZ24">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BA24">
         <v>38</v>
       </c>
       <c r="BB24">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BC24">
         <v>32</v>
       </c>
       <c r="BD24">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BE24">
         <v>10.5</v>
       </c>
       <c r="BF24">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BG24">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH24">
         <v>2.9</v>
       </c>
       <c r="BI24">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BJ24">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK24">
         <v>5.5</v>
@@ -7536,25 +7536,25 @@
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN24">
         <v>6.6</v>
       </c>
       <c r="BO24">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BP24">
         <v>32</v>
       </c>
       <c r="BQ24">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR24">
         <v>1000</v>
       </c>
       <c r="BS24">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT24">
         <v>5.5</v>
@@ -7566,19 +7566,19 @@
         <v>23</v>
       </c>
       <c r="BW24">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BX24">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY24">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BZ24">
         <v>46</v>
       </c>
       <c r="CA24">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="CB24" t="s">
         <v>475</v>
@@ -7601,16 +7601,16 @@
         <v>351</v>
       </c>
       <c r="F25">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="G25">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="H25">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I25">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="J25">
         <v>3.4</v>
@@ -7625,7 +7625,7 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>3.55</v>
+        <v>1.1</v>
       </c>
       <c r="O25">
         <v>1.27</v>
@@ -7637,22 +7637,22 @@
         <v>1.84</v>
       </c>
       <c r="R25">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="S25">
         <v>3</v>
       </c>
       <c r="T25">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="U25">
         <v>1.11</v>
       </c>
       <c r="V25">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W25">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -7843,22 +7843,22 @@
         <v>352</v>
       </c>
       <c r="F26">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="G26">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="H26">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="I26">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="J26">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K26">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -7867,16 +7867,16 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O26">
         <v>1.22</v>
       </c>
       <c r="P26">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q26">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R26">
         <v>1.39</v>
@@ -7885,16 +7885,16 @@
         <v>2.48</v>
       </c>
       <c r="T26">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="U26">
-        <v>1.11</v>
+        <v>2.14</v>
       </c>
       <c r="V26">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="W26">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -8085,7 +8085,7 @@
         <v>353</v>
       </c>
       <c r="F27">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="G27">
         <v>3.45</v>
@@ -8094,7 +8094,7 @@
         <v>2.34</v>
       </c>
       <c r="I27">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="J27">
         <v>3.5</v>
@@ -8118,13 +8118,13 @@
         <v>1.87</v>
       </c>
       <c r="Q27">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R27">
         <v>1.31</v>
       </c>
       <c r="S27">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="T27">
         <v>1.73</v>
@@ -8133,10 +8133,10 @@
         <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W27">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -8327,16 +8327,16 @@
         <v>354</v>
       </c>
       <c r="F28">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="G28">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="H28">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="I28">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J28">
         <v>3.15</v>
@@ -8351,19 +8351,19 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>2.82</v>
+        <v>1.01</v>
       </c>
       <c r="O28">
         <v>1.39</v>
       </c>
       <c r="P28">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q28">
         <v>2.28</v>
       </c>
       <c r="R28">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S28">
         <v>4.2</v>
@@ -8375,10 +8375,10 @@
         <v>1.86</v>
       </c>
       <c r="V28">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W28">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -8569,22 +8569,22 @@
         <v>355</v>
       </c>
       <c r="F29">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="G29">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="H29">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="I29">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="J29">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K29">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -8596,19 +8596,19 @@
         <v>3.6</v>
       </c>
       <c r="O29">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P29">
         <v>1.89</v>
       </c>
       <c r="Q29">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="R29">
         <v>1.34</v>
       </c>
       <c r="S29">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T29">
         <v>1.87</v>
@@ -8617,22 +8617,22 @@
         <v>1.98</v>
       </c>
       <c r="V29">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="W29">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="X29">
         <v>17.5</v>
       </c>
       <c r="Y29">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z29">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AA29">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB29">
         <v>8.6</v>
@@ -8641,7 +8641,7 @@
         <v>10.5</v>
       </c>
       <c r="AD29">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE29">
         <v>75</v>
@@ -8668,67 +8668,67 @@
         <v>46</v>
       </c>
       <c r="AM29">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN29">
         <v>13</v>
       </c>
       <c r="AO29">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP29">
         <v>10.5</v>
       </c>
       <c r="AQ29">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR29">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AS29">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AT29">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU29">
-        <v>6.4</v>
+        <v>3.65</v>
       </c>
       <c r="AV29">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="AW29">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AX29">
-        <v>8</v>
+        <v>3.7</v>
       </c>
       <c r="AY29">
         <v>7.6</v>
       </c>
       <c r="AZ29">
+        <v>4.6</v>
+      </c>
+      <c r="BA29">
+        <v>5.3</v>
+      </c>
+      <c r="BB29">
+        <v>4.5</v>
+      </c>
+      <c r="BC29">
         <v>14.5</v>
       </c>
-      <c r="BA29">
-        <v>1.01</v>
-      </c>
-      <c r="BB29">
-        <v>14</v>
-      </c>
-      <c r="BC29">
-        <v>14</v>
-      </c>
       <c r="BD29">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE29">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF29">
-        <v>9.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="BG29">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BH29">
         <v>4.1</v>
@@ -9295,22 +9295,22 @@
         <v>358</v>
       </c>
       <c r="F32">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G32">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H32">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="I32">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J32">
         <v>3.55</v>
       </c>
       <c r="K32">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="L32">
         <v>1.01</v>
@@ -9343,10 +9343,10 @@
         <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W32">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -9567,7 +9567,7 @@
         <v>1.33</v>
       </c>
       <c r="P33">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q33">
         <v>2.08</v>
@@ -10021,16 +10021,16 @@
         <v>361</v>
       </c>
       <c r="F35">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G35">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H35">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="I35">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="J35">
         <v>4.5</v>
@@ -10039,73 +10039,73 @@
         <v>4.7</v>
       </c>
       <c r="L35">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="M35">
         <v>1.02</v>
       </c>
       <c r="N35">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O35">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P35">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="Q35">
         <v>1.5</v>
       </c>
       <c r="R35">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="S35">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T35">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="U35">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="V35">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="W35">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X35">
         <v>29</v>
       </c>
       <c r="Y35">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Z35">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA35">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB35">
         <v>30</v>
       </c>
       <c r="AC35">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD35">
         <v>11</v>
       </c>
       <c r="AE35">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AF35">
         <v>40</v>
       </c>
       <c r="AG35">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AH35">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI35">
         <v>25</v>
@@ -10117,22 +10117,22 @@
         <v>44</v>
       </c>
       <c r="AL35">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM35">
         <v>60</v>
       </c>
       <c r="AN35">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AO35">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AP35">
         <v>22</v>
       </c>
       <c r="AQ35">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR35">
         <v>13</v>
@@ -10165,7 +10165,7 @@
         <v>21</v>
       </c>
       <c r="BB35">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BC35">
         <v>36</v>
@@ -10174,13 +10174,13 @@
         <v>34</v>
       </c>
       <c r="BE35">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BF35">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BG35">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH35">
         <v>1000</v>
@@ -10529,7 +10529,7 @@
         <v>1.06</v>
       </c>
       <c r="N37">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O37">
         <v>1.29</v>
@@ -10538,19 +10538,19 @@
         <v>2.1</v>
       </c>
       <c r="Q37">
+        <v>1.85</v>
+      </c>
+      <c r="R37">
+        <v>1.43</v>
+      </c>
+      <c r="S37">
+        <v>3.1</v>
+      </c>
+      <c r="T37">
         <v>1.81</v>
       </c>
-      <c r="R37">
-        <v>1.42</v>
-      </c>
-      <c r="S37">
-        <v>3.05</v>
-      </c>
-      <c r="T37">
-        <v>1.79</v>
-      </c>
       <c r="U37">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V37">
         <v>1.24</v>
@@ -10571,7 +10571,7 @@
         <v>120</v>
       </c>
       <c r="AB37">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC37">
         <v>8.800000000000001</v>
@@ -10580,10 +10580,10 @@
         <v>19</v>
       </c>
       <c r="AE37">
-        <v>60</v>
+        <v>540</v>
       </c>
       <c r="AF37">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG37">
         <v>10.5</v>
@@ -10592,7 +10592,7 @@
         <v>18.5</v>
       </c>
       <c r="AI37">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ37">
         <v>19.5</v>
@@ -10604,16 +10604,16 @@
         <v>34</v>
       </c>
       <c r="AM37">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN37">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO37">
         <v>65</v>
       </c>
       <c r="AP37">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ37">
         <v>16.5</v>
@@ -10622,7 +10622,7 @@
         <v>34</v>
       </c>
       <c r="AS37">
-        <v>12.5</v>
+        <v>40</v>
       </c>
       <c r="AT37">
         <v>8.800000000000001</v>
@@ -10634,13 +10634,13 @@
         <v>17</v>
       </c>
       <c r="AW37">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="AX37">
         <v>10.5</v>
       </c>
       <c r="AY37">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ37">
         <v>17</v>
@@ -10658,7 +10658,7 @@
         <v>29</v>
       </c>
       <c r="BE37">
-        <v>12.5</v>
+        <v>38</v>
       </c>
       <c r="BF37">
         <v>9.6</v>
@@ -10989,7 +10989,7 @@
         <v>365</v>
       </c>
       <c r="F39">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G39">
         <v>3.8</v>
@@ -10998,7 +10998,7 @@
         <v>2.02</v>
       </c>
       <c r="I39">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="J39">
         <v>4.1</v>
@@ -11019,10 +11019,10 @@
         <v>1.17</v>
       </c>
       <c r="P39">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="Q39">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="R39">
         <v>1.63</v>
@@ -11040,13 +11040,13 @@
         <v>1.89</v>
       </c>
       <c r="W39">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X39">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="Y39">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="Z39">
         <v>19.5</v>
@@ -11058,7 +11058,7 @@
         <v>22</v>
       </c>
       <c r="AC39">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AD39">
         <v>13.5</v>
@@ -11070,7 +11070,7 @@
         <v>32</v>
       </c>
       <c r="AG39">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AH39">
         <v>17.5</v>
@@ -11091,7 +11091,7 @@
         <v>60</v>
       </c>
       <c r="AN39">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AO39">
         <v>9.800000000000001</v>
@@ -11103,7 +11103,7 @@
         <v>11.5</v>
       </c>
       <c r="AR39">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AS39">
         <v>21</v>
@@ -11115,13 +11115,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV39">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AW39">
         <v>16</v>
       </c>
       <c r="AX39">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="AY39">
         <v>13</v>
@@ -11133,16 +11133,16 @@
         <v>20</v>
       </c>
       <c r="BB39">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC39">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BD39">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="BE39">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BF39">
         <v>16.5</v>
@@ -11279,10 +11279,10 @@
         <v>1.11</v>
       </c>
       <c r="V40">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W40">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X40">
         <v>1000</v>
@@ -11473,7 +11473,7 @@
         <v>367</v>
       </c>
       <c r="F41">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="G41">
         <v>1.4</v>
@@ -11715,7 +11715,7 @@
         <v>368</v>
       </c>
       <c r="F42">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G42">
         <v>1.69</v>
@@ -12441,10 +12441,10 @@
         <v>371</v>
       </c>
       <c r="F45">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="G45">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H45">
         <v>3.2</v>
@@ -12465,7 +12465,7 @@
         <v>1.03</v>
       </c>
       <c r="N45">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="O45">
         <v>1.32</v>
@@ -12474,25 +12474,25 @@
         <v>1.81</v>
       </c>
       <c r="Q45">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="R45">
         <v>1.37</v>
       </c>
       <c r="S45">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T45">
         <v>1.69</v>
       </c>
       <c r="U45">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="V45">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W45">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X45">
         <v>36</v>
@@ -12549,58 +12549,58 @@
         <v>1000</v>
       </c>
       <c r="AP45">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AQ45">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AR45">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AS45">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AT45">
         <v>1.19</v>
       </c>
       <c r="AU45">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AV45">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AW45">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AX45">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AY45">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AZ45">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BA45">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BB45">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BC45">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BD45">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BE45">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BF45">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BG45">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BH45">
         <v>1000</v>
@@ -12686,7 +12686,7 @@
         <v>1.93</v>
       </c>
       <c r="G46">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H46">
         <v>2.92</v>
@@ -12695,10 +12695,10 @@
         <v>4.1</v>
       </c>
       <c r="J46">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K46">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -12734,7 +12734,7 @@
         <v>1.32</v>
       </c>
       <c r="W46">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X46">
         <v>1000</v>
@@ -12943,7 +12943,7 @@
         <v>4.4</v>
       </c>
       <c r="L47">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M47">
         <v>1.01</v>
@@ -13167,7 +13167,7 @@
         <v>374</v>
       </c>
       <c r="F48">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="G48">
         <v>1.69</v>
@@ -13421,10 +13421,10 @@
         <v>3.55</v>
       </c>
       <c r="J49">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K49">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="L49">
         <v>1.01</v>
@@ -13436,7 +13436,7 @@
         <v>5.5</v>
       </c>
       <c r="O49">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P49">
         <v>2.38</v>
@@ -13454,7 +13454,7 @@
         <v>1.44</v>
       </c>
       <c r="U49">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="V49">
         <v>1.39</v>
@@ -13475,13 +13475,13 @@
         <v>55</v>
       </c>
       <c r="AB49">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AC49">
         <v>12</v>
       </c>
       <c r="AD49">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AE49">
         <v>32</v>
@@ -13490,7 +13490,7 @@
         <v>22</v>
       </c>
       <c r="AG49">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AH49">
         <v>16</v>
@@ -13502,10 +13502,10 @@
         <v>34</v>
       </c>
       <c r="AK49">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL49">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM49">
         <v>60</v>
@@ -13678,7 +13678,7 @@
         <v>2.1</v>
       </c>
       <c r="O50">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="P50">
         <v>1.32</v>
@@ -13696,7 +13696,7 @@
         <v>1.11</v>
       </c>
       <c r="U50">
-        <v>1.11</v>
+        <v>1.53</v>
       </c>
       <c r="V50">
         <v>1.38</v>
@@ -13896,7 +13896,7 @@
         <v>2.32</v>
       </c>
       <c r="G51">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="H51">
         <v>3.3</v>
@@ -13905,10 +13905,10 @@
         <v>3.4</v>
       </c>
       <c r="J51">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="K51">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L51">
         <v>1.12</v>
@@ -13926,7 +13926,7 @@
         <v>1.94</v>
       </c>
       <c r="Q51">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="R51">
         <v>1.37</v>
@@ -13944,7 +13944,7 @@
         <v>1.41</v>
       </c>
       <c r="W51">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="X51">
         <v>15</v>
@@ -13968,7 +13968,7 @@
         <v>14.5</v>
       </c>
       <c r="AE51">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF51">
         <v>15.5</v>
@@ -13983,13 +13983,13 @@
         <v>48</v>
       </c>
       <c r="AJ51">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK51">
         <v>32</v>
       </c>
       <c r="AL51">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AM51">
         <v>110</v>
@@ -14147,7 +14147,7 @@
         <v>870</v>
       </c>
       <c r="J52">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K52">
         <v>500</v>
@@ -14649,7 +14649,7 @@
         <v>1.36</v>
       </c>
       <c r="P54">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="Q54">
         <v>1.36</v>
@@ -14667,10 +14667,10 @@
         <v>1.11</v>
       </c>
       <c r="V54">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W54">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X54">
         <v>1000</v>
@@ -14873,10 +14873,10 @@
         <v>5.5</v>
       </c>
       <c r="J55">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K55">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="L55">
         <v>1.01</v>
@@ -14885,7 +14885,7 @@
         <v>1.04</v>
       </c>
       <c r="N55">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="O55">
         <v>1.22</v>
@@ -14900,7 +14900,7 @@
         <v>1.46</v>
       </c>
       <c r="S55">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T55">
         <v>1.6</v>
@@ -15351,7 +15351,7 @@
         <v>2.46</v>
       </c>
       <c r="H57">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="I57">
         <v>3.9</v>
@@ -15360,7 +15360,7 @@
         <v>3.45</v>
       </c>
       <c r="K57">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="L57">
         <v>1.01</v>
@@ -16074,7 +16074,7 @@
         <v>1.52</v>
       </c>
       <c r="G60">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="H60">
         <v>3.55</v>
@@ -16083,7 +16083,7 @@
         <v>7.4</v>
       </c>
       <c r="J60">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="K60">
         <v>5.9</v>
@@ -16104,7 +16104,7 @@
         <v>2.2</v>
       </c>
       <c r="Q60">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="R60">
         <v>1.45</v>
@@ -16113,16 +16113,16 @@
         <v>2.16</v>
       </c>
       <c r="T60">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="U60">
-        <v>2.12</v>
+        <v>1.96</v>
       </c>
       <c r="V60">
         <v>1.16</v>
       </c>
       <c r="W60">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="X60">
         <v>1000</v>
@@ -16254,7 +16254,7 @@
         <v>6.2</v>
       </c>
       <c r="BO60">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BP60">
         <v>14.5</v>
@@ -16313,19 +16313,19 @@
         <v>387</v>
       </c>
       <c r="F61">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G61">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="H61">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="I61">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="J61">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K61">
         <v>4</v>
@@ -16349,7 +16349,7 @@
         <v>1.74</v>
       </c>
       <c r="R61">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S61">
         <v>2.84</v>
@@ -16361,10 +16361,10 @@
         <v>2.42</v>
       </c>
       <c r="V61">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="W61">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X61">
         <v>19</v>
@@ -16379,7 +16379,7 @@
         <v>42</v>
       </c>
       <c r="AB61">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC61">
         <v>8.800000000000001</v>
@@ -16418,7 +16418,7 @@
         <v>23</v>
       </c>
       <c r="AO61">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="AP61">
         <v>14</v>
@@ -16454,13 +16454,13 @@
         <v>13.5</v>
       </c>
       <c r="BA61">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BB61">
         <v>7.4</v>
       </c>
       <c r="BC61">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BD61">
         <v>7.2</v>
@@ -17075,13 +17075,13 @@
         <v>1.72</v>
       </c>
       <c r="R64">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S64">
         <v>2.82</v>
       </c>
       <c r="T64">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U64">
         <v>2.32</v>
@@ -17284,10 +17284,10 @@
         <v>2.38</v>
       </c>
       <c r="G65">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="H65">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I65">
         <v>3.2</v>
@@ -17305,34 +17305,34 @@
         <v>1.05</v>
       </c>
       <c r="N65">
-        <v>2.94</v>
+        <v>4</v>
       </c>
       <c r="O65">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P65">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="Q65">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R65">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S65">
         <v>2.78</v>
       </c>
       <c r="T65">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="U65">
         <v>2.4</v>
       </c>
       <c r="V65">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W65">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X65">
         <v>1000</v>
@@ -17347,13 +17347,13 @@
         <v>1000</v>
       </c>
       <c r="AB65">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AC65">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD65">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE65">
         <v>1000</v>
@@ -17389,58 +17389,58 @@
         <v>1000</v>
       </c>
       <c r="AP65">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AQ65">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AR65">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AS65">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AT65">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AU65">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AV65">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AW65">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AX65">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AY65">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AZ65">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BA65">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BB65">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BC65">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BD65">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BE65">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BF65">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BG65">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BH65">
         <v>1000</v>
@@ -17529,10 +17529,10 @@
         <v>1.53</v>
       </c>
       <c r="H66">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I66">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J66">
         <v>5</v>
@@ -17547,16 +17547,16 @@
         <v>1.03</v>
       </c>
       <c r="N66">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O66">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P66">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="Q66">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="R66">
         <v>1.62</v>
@@ -17565,10 +17565,10 @@
         <v>2.46</v>
       </c>
       <c r="T66">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U66">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V66">
         <v>1.16</v>
@@ -17586,25 +17586,25 @@
         <v>65</v>
       </c>
       <c r="AA66">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AB66">
         <v>12</v>
       </c>
       <c r="AC66">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AD66">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE66">
         <v>90</v>
       </c>
       <c r="AF66">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG66">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH66">
         <v>22</v>
@@ -17613,7 +17613,7 @@
         <v>75</v>
       </c>
       <c r="AJ66">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AK66">
         <v>15.5</v>
@@ -17625,7 +17625,7 @@
         <v>100</v>
       </c>
       <c r="AN66">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AO66">
         <v>85</v>
@@ -17634,28 +17634,28 @@
         <v>21</v>
       </c>
       <c r="AQ66">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR66">
-        <v>8</v>
+        <v>9.4</v>
       </c>
       <c r="AS66">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AT66">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AU66">
         <v>10</v>
       </c>
       <c r="AV66">
-        <v>6.8</v>
+        <v>19.5</v>
       </c>
       <c r="AW66">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX66">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AY66">
         <v>9</v>
@@ -17664,25 +17664,25 @@
         <v>17.5</v>
       </c>
       <c r="BA66">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BB66">
         <v>12</v>
       </c>
       <c r="BC66">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BD66">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BE66">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF66">
         <v>5.3</v>
       </c>
       <c r="BG66">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH66">
         <v>1000</v>
@@ -17798,13 +17798,13 @@
         <v>2.52</v>
       </c>
       <c r="Q67">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="R67">
         <v>1.6</v>
       </c>
       <c r="S67">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="T67">
         <v>1.56</v>
@@ -18010,7 +18010,7 @@
         <v>3.8</v>
       </c>
       <c r="G68">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H68">
         <v>2</v>
@@ -18058,7 +18058,7 @@
         <v>1.98</v>
       </c>
       <c r="W68">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X68">
         <v>1000</v>
@@ -18249,7 +18249,7 @@
         <v>395</v>
       </c>
       <c r="F69">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="G69">
         <v>1.73</v>
@@ -18261,16 +18261,16 @@
         <v>5.3</v>
       </c>
       <c r="J69">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K69">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L69">
         <v>1.01</v>
       </c>
       <c r="M69">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N69">
         <v>6.6</v>
@@ -18279,28 +18279,28 @@
         <v>1.15</v>
       </c>
       <c r="P69">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="Q69">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R69">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="S69">
         <v>2.12</v>
       </c>
       <c r="T69">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="U69">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="V69">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W69">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="X69">
         <v>32</v>
@@ -18309,7 +18309,7 @@
         <v>30</v>
       </c>
       <c r="Z69">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA69">
         <v>130</v>
@@ -18318,7 +18318,7 @@
         <v>15.5</v>
       </c>
       <c r="AC69">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AD69">
         <v>21</v>
@@ -18357,16 +18357,16 @@
         <v>34</v>
       </c>
       <c r="AP69">
+        <v>27</v>
+      </c>
+      <c r="AQ69">
+        <v>8.4</v>
+      </c>
+      <c r="AR69">
         <v>9.199999999999999</v>
       </c>
-      <c r="AQ69">
-        <v>9</v>
-      </c>
-      <c r="AR69">
-        <v>10</v>
-      </c>
       <c r="AS69">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT69">
         <v>13</v>
@@ -18378,7 +18378,7 @@
         <v>18</v>
       </c>
       <c r="AW69">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AX69">
         <v>12.5</v>
@@ -18390,7 +18390,7 @@
         <v>14</v>
       </c>
       <c r="BA69">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BB69">
         <v>16</v>
@@ -18402,13 +18402,13 @@
         <v>20</v>
       </c>
       <c r="BE69">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BF69">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BG69">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH69">
         <v>1000</v>
@@ -18491,40 +18491,40 @@
         <v>396</v>
       </c>
       <c r="F70">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G70">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="H70">
         <v>5.3</v>
       </c>
       <c r="I70">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J70">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K70">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L70">
         <v>1.01</v>
       </c>
       <c r="M70">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N70">
         <v>2.36</v>
       </c>
       <c r="O70">
-        <v>1.44</v>
+        <v>1.11</v>
       </c>
       <c r="P70">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q70">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="R70">
         <v>1.17</v>
@@ -18536,13 +18536,13 @@
         <v>1.11</v>
       </c>
       <c r="U70">
-        <v>1.11</v>
+        <v>1.59</v>
       </c>
       <c r="V70">
         <v>1.18</v>
       </c>
       <c r="W70">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="X70">
         <v>1000</v>
@@ -18975,13 +18975,13 @@
         <v>398</v>
       </c>
       <c r="F72">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G72">
         <v>4.9</v>
       </c>
       <c r="H72">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="I72">
         <v>2.24</v>
@@ -18990,7 +18990,7 @@
         <v>3.45</v>
       </c>
       <c r="K72">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="L72">
         <v>1.01</v>
@@ -19492,10 +19492,10 @@
         <v>2.22</v>
       </c>
       <c r="Q74">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R74">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="S74">
         <v>2.8</v>
@@ -19516,10 +19516,10 @@
         <v>23</v>
       </c>
       <c r="Y74">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z74">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AA74">
         <v>29</v>
@@ -19528,10 +19528,10 @@
         <v>20</v>
       </c>
       <c r="AC74">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="AD74">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AE74">
         <v>24</v>
@@ -19564,13 +19564,13 @@
         <v>38</v>
       </c>
       <c r="AO74">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AP74">
         <v>17</v>
       </c>
       <c r="AQ74">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR74">
         <v>12.5</v>
@@ -19591,7 +19591,7 @@
         <v>17.5</v>
       </c>
       <c r="AX74">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AY74">
         <v>13.5</v>
@@ -19600,25 +19600,25 @@
         <v>14.5</v>
       </c>
       <c r="BA74">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BB74">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BC74">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="BD74">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE74">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BF74">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BG74">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BH74">
         <v>1000</v>
@@ -19701,22 +19701,22 @@
         <v>401</v>
       </c>
       <c r="F75">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="G75">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="H75">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I75">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J75">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K75">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L75">
         <v>1.01</v>
@@ -19728,28 +19728,28 @@
         <v>4.4</v>
       </c>
       <c r="O75">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P75">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q75">
+        <v>1.76</v>
+      </c>
+      <c r="R75">
+        <v>1.48</v>
+      </c>
+      <c r="S75">
+        <v>2.88</v>
+      </c>
+      <c r="T75">
         <v>1.74</v>
       </c>
-      <c r="R75">
-        <v>1.46</v>
-      </c>
-      <c r="S75">
-        <v>2.8</v>
-      </c>
-      <c r="T75">
-        <v>1.72</v>
-      </c>
       <c r="U75">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V75">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W75">
         <v>2.2</v>
@@ -19767,10 +19767,10 @@
         <v>140</v>
       </c>
       <c r="AB75">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC75">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD75">
         <v>24</v>
@@ -19779,10 +19779,10 @@
         <v>75</v>
       </c>
       <c r="AF75">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG75">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH75">
         <v>22</v>
@@ -19803,7 +19803,7 @@
         <v>110</v>
       </c>
       <c r="AN75">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AO75">
         <v>75</v>
@@ -19815,13 +19815,13 @@
         <v>17</v>
       </c>
       <c r="AR75">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AS75">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AT75">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AU75">
         <v>8</v>
@@ -19830,19 +19830,19 @@
         <v>16.5</v>
       </c>
       <c r="AW75">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AX75">
         <v>10</v>
       </c>
       <c r="AY75">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ75">
         <v>15</v>
       </c>
       <c r="BA75">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BB75">
         <v>15.5</v>
@@ -19851,16 +19851,16 @@
         <v>14.5</v>
       </c>
       <c r="BD75">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="BE75">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="BF75">
-        <v>7.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG75">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BH75">
         <v>1000</v>
@@ -20430,10 +20430,10 @@
         <v>2.04</v>
       </c>
       <c r="G78">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H78">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I78">
         <v>3.55</v>
@@ -20442,7 +20442,7 @@
         <v>4.1</v>
       </c>
       <c r="K78">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L78">
         <v>1.01</v>
@@ -20451,16 +20451,16 @@
         <v>1.01</v>
       </c>
       <c r="N78">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="O78">
         <v>1.13</v>
       </c>
       <c r="P78">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="Q78">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
       <c r="R78">
         <v>1.62</v>
@@ -20469,7 +20469,7 @@
         <v>1.98</v>
       </c>
       <c r="T78">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="U78">
         <v>1.11</v>
@@ -20478,7 +20478,7 @@
         <v>1.39</v>
       </c>
       <c r="W78">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="X78">
         <v>1000</v>
@@ -20684,7 +20684,7 @@
         <v>3.25</v>
       </c>
       <c r="K79">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L79">
         <v>1.01</v>
@@ -20723,10 +20723,10 @@
         <v>1.5</v>
       </c>
       <c r="X79">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y79">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z79">
         <v>22</v>
@@ -20786,7 +20786,7 @@
         <v>15.5</v>
       </c>
       <c r="AS79">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT79">
         <v>9</v>
@@ -20798,7 +20798,7 @@
         <v>10.5</v>
       </c>
       <c r="AW79">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX79">
         <v>15.5</v>
@@ -20810,25 +20810,25 @@
         <v>15</v>
       </c>
       <c r="BA79">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB79">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BC79">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BD79">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE79">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BF79">
+        <v>5</v>
+      </c>
+      <c r="BG79">
         <v>4.9</v>
-      </c>
-      <c r="BG79">
-        <v>4.8</v>
       </c>
       <c r="BH79">
         <v>1000</v>
@@ -21395,19 +21395,19 @@
         <v>408</v>
       </c>
       <c r="F82">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="G82">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H82">
         <v>3.7</v>
       </c>
       <c r="I82">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J82">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="K82">
         <v>4.5</v>
@@ -21419,19 +21419,19 @@
         <v>1.01</v>
       </c>
       <c r="N82">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="O82">
         <v>1.18</v>
       </c>
       <c r="P82">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="Q82">
         <v>1.54</v>
       </c>
       <c r="R82">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="S82">
         <v>2.34</v>
@@ -21443,10 +21443,10 @@
         <v>2.5</v>
       </c>
       <c r="V82">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W82">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X82">
         <v>27</v>
@@ -21458,7 +21458,7 @@
         <v>34</v>
       </c>
       <c r="AA82">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB82">
         <v>14.5</v>
@@ -21482,7 +21482,7 @@
         <v>16.5</v>
       </c>
       <c r="AI82">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ82">
         <v>25</v>
@@ -21494,7 +21494,7 @@
         <v>28</v>
       </c>
       <c r="AM82">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AN82">
         <v>9.4</v>
@@ -21637,22 +21637,22 @@
         <v>409</v>
       </c>
       <c r="F83">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G83">
         <v>1.51</v>
       </c>
       <c r="H83">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="I83">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J83">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="K83">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="L83">
         <v>1.01</v>
@@ -21661,22 +21661,22 @@
         <v>1.01</v>
       </c>
       <c r="N83">
-        <v>3.15</v>
+        <v>1.1</v>
       </c>
       <c r="O83">
         <v>1.09</v>
       </c>
       <c r="P83">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q83">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="R83">
         <v>1.9</v>
       </c>
       <c r="S83">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="T83">
         <v>1.5</v>
@@ -21685,7 +21685,7 @@
         <v>1.11</v>
       </c>
       <c r="V83">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W83">
         <v>2.96</v>
@@ -21882,19 +21882,19 @@
         <v>2.44</v>
       </c>
       <c r="G84">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="H84">
         <v>2.44</v>
       </c>
       <c r="I84">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J84">
         <v>4.1</v>
       </c>
       <c r="K84">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L84">
         <v>1.01</v>
@@ -21915,7 +21915,7 @@
         <v>1.37</v>
       </c>
       <c r="R84">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="S84">
         <v>1.91</v>
@@ -21924,13 +21924,13 @@
         <v>1.38</v>
       </c>
       <c r="U84">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="V84">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W84">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X84">
         <v>42</v>
@@ -21957,37 +21957,37 @@
         <v>24</v>
       </c>
       <c r="AF84">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG84">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH84">
         <v>14.5</v>
       </c>
       <c r="AI84">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ84">
+        <v>38</v>
+      </c>
+      <c r="AK84">
+        <v>23</v>
+      </c>
+      <c r="AL84">
+        <v>25</v>
+      </c>
+      <c r="AM84">
         <v>40</v>
       </c>
-      <c r="AK84">
-        <v>24</v>
-      </c>
-      <c r="AL84">
-        <v>26</v>
-      </c>
-      <c r="AM84">
-        <v>42</v>
-      </c>
       <c r="AN84">
+        <v>10.5</v>
+      </c>
+      <c r="AO84">
         <v>11</v>
       </c>
-      <c r="AO84">
-        <v>10.5</v>
-      </c>
       <c r="AP84">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ84">
         <v>16.5</v>
@@ -21996,7 +21996,7 @@
         <v>18.5</v>
       </c>
       <c r="AS84">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AT84">
         <v>16.5</v>
@@ -22023,7 +22023,7 @@
         <v>17.5</v>
       </c>
       <c r="BB84">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BC84">
         <v>16.5</v>
@@ -22032,10 +22032,10 @@
         <v>17.5</v>
       </c>
       <c r="BE84">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF84">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BG84">
         <v>8.4</v>
@@ -22605,31 +22605,31 @@
         <v>413</v>
       </c>
       <c r="F87">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="G87">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="H87">
         <v>2.46</v>
       </c>
       <c r="I87">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J87">
         <v>3.5</v>
       </c>
       <c r="K87">
-        <v>5.4</v>
+        <v>8</v>
       </c>
       <c r="L87">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="M87">
         <v>1.04</v>
       </c>
       <c r="N87">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="O87">
         <v>1.29</v>
@@ -22653,10 +22653,10 @@
         <v>1.11</v>
       </c>
       <c r="V87">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W87">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="X87">
         <v>1000</v>
@@ -22850,43 +22850,43 @@
         <v>2.8</v>
       </c>
       <c r="G88">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="H88">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I88">
         <v>2.78</v>
       </c>
       <c r="J88">
-        <v>2.82</v>
+        <v>1.1</v>
       </c>
       <c r="K88">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="L88">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="M88">
         <v>1.01</v>
       </c>
       <c r="N88">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="O88">
         <v>1.31</v>
       </c>
       <c r="P88">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="Q88">
         <v>1.81</v>
       </c>
       <c r="R88">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S88">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="T88">
         <v>1.01</v>
@@ -22898,7 +22898,7 @@
         <v>1.56</v>
       </c>
       <c r="W88">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="X88">
         <v>1000</v>
@@ -23089,22 +23089,22 @@
         <v>415</v>
       </c>
       <c r="F89">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="G89">
-        <v>2.8</v>
+        <v>2.54</v>
       </c>
       <c r="H89">
+        <v>3.4</v>
+      </c>
+      <c r="I89">
+        <v>3.9</v>
+      </c>
+      <c r="J89">
+        <v>3</v>
+      </c>
+      <c r="K89">
         <v>3.25</v>
-      </c>
-      <c r="I89">
-        <v>4.6</v>
-      </c>
-      <c r="J89">
-        <v>2.9</v>
-      </c>
-      <c r="K89">
-        <v>3.3</v>
       </c>
       <c r="L89">
         <v>0</v>
@@ -23337,7 +23337,7 @@
         <v>2.48</v>
       </c>
       <c r="H90">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I90">
         <v>3.35</v>
@@ -23349,7 +23349,7 @@
         <v>3.65</v>
       </c>
       <c r="L90">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="M90">
         <v>1.06</v>
@@ -23364,7 +23364,7 @@
         <v>2</v>
       </c>
       <c r="Q90">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R90">
         <v>1.39</v>
@@ -23373,7 +23373,7 @@
         <v>3.1</v>
       </c>
       <c r="T90">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U90">
         <v>2.2</v>
@@ -23382,7 +23382,7 @@
         <v>1.42</v>
       </c>
       <c r="W90">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="X90">
         <v>16.5</v>
@@ -23445,7 +23445,7 @@
         <v>12</v>
       </c>
       <c r="AR90">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS90">
         <v>44</v>
@@ -23457,7 +23457,7 @@
         <v>7.2</v>
       </c>
       <c r="AV90">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW90">
         <v>30</v>
@@ -23579,22 +23579,22 @@
         <v>2.56</v>
       </c>
       <c r="H91">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I91">
         <v>4.4</v>
       </c>
       <c r="J91">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K91">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L91">
         <v>1.5</v>
       </c>
       <c r="M91">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N91">
         <v>2.38</v>
@@ -23606,13 +23606,13 @@
         <v>1.43</v>
       </c>
       <c r="Q91">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="R91">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="S91">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="T91">
         <v>2.26</v>
@@ -23639,7 +23639,7 @@
         <v>130</v>
       </c>
       <c r="AB91">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC91">
         <v>7.4</v>
@@ -23690,7 +23690,7 @@
         <v>19</v>
       </c>
       <c r="AS91">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT91">
         <v>5.1</v>
@@ -23702,7 +23702,7 @@
         <v>13.5</v>
       </c>
       <c r="AW91">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AX91">
         <v>9.6</v>
@@ -23714,25 +23714,25 @@
         <v>19</v>
       </c>
       <c r="BA91">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB91">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BC91">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD91">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BE91">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BF91">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG91">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH91">
         <v>1000</v>
@@ -23842,7 +23842,7 @@
         <v>3.15</v>
       </c>
       <c r="O92">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P92">
         <v>2.04</v>
@@ -23851,16 +23851,16 @@
         <v>1.76</v>
       </c>
       <c r="R92">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="S92">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T92">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="U92">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="V92">
         <v>1.9</v>
@@ -24057,19 +24057,19 @@
         <v>419</v>
       </c>
       <c r="F93">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="G93">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H93">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="I93">
         <v>2.62</v>
       </c>
       <c r="J93">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K93">
         <v>4.2</v>
@@ -24108,7 +24108,7 @@
         <v>1.61</v>
       </c>
       <c r="W93">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X93">
         <v>1000</v>
@@ -24302,10 +24302,10 @@
         <v>1.27</v>
       </c>
       <c r="G94">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="H94">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="I94">
         <v>16</v>
@@ -24335,7 +24335,7 @@
         <v>1.4</v>
       </c>
       <c r="R94">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="S94">
         <v>2.18</v>
@@ -24350,7 +24350,7 @@
         <v>1.06</v>
       </c>
       <c r="W94">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="X94">
         <v>46</v>
@@ -24446,7 +24446,7 @@
         <v>1.62</v>
       </c>
       <c r="BC94">
-        <v>9.4</v>
+        <v>1.66</v>
       </c>
       <c r="BD94">
         <v>1.75</v>
@@ -24544,13 +24544,13 @@
         <v>1.73</v>
       </c>
       <c r="G95">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H95">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I95">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J95">
         <v>3.6</v>
@@ -24568,7 +24568,7 @@
         <v>3.15</v>
       </c>
       <c r="O95">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P95">
         <v>1.72</v>
@@ -24580,7 +24580,7 @@
         <v>1.27</v>
       </c>
       <c r="S95">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T95">
         <v>2</v>
@@ -24592,10 +24592,10 @@
         <v>1.19</v>
       </c>
       <c r="W95">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="X95">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y95">
         <v>19.5</v>
@@ -24607,7 +24607,7 @@
         <v>190</v>
       </c>
       <c r="AB95">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC95">
         <v>8.800000000000001</v>
@@ -24619,7 +24619,7 @@
         <v>110</v>
       </c>
       <c r="AF95">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG95">
         <v>11</v>
@@ -24631,7 +24631,7 @@
         <v>120</v>
       </c>
       <c r="AJ95">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AK95">
         <v>26</v>
@@ -24643,7 +24643,7 @@
         <v>190</v>
       </c>
       <c r="AN95">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AO95">
         <v>150</v>
@@ -24655,10 +24655,10 @@
         <v>13.5</v>
       </c>
       <c r="AR95">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AS95">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT95">
         <v>6.2</v>
@@ -24670,7 +24670,7 @@
         <v>18.5</v>
       </c>
       <c r="AW95">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AX95">
         <v>8.6</v>
@@ -24682,7 +24682,7 @@
         <v>19</v>
       </c>
       <c r="BA95">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB95">
         <v>16.5</v>
@@ -24691,16 +24691,16 @@
         <v>18</v>
       </c>
       <c r="BD95">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="BE95">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF95">
         <v>11</v>
       </c>
       <c r="BG95">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH95">
         <v>1000</v>
@@ -24792,10 +24792,10 @@
         <v>5.2</v>
       </c>
       <c r="I96">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J96">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K96">
         <v>5.3</v>
@@ -24816,22 +24816,22 @@
         <v>2.32</v>
       </c>
       <c r="Q96">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R96">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="S96">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T96">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U96">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="V96">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W96">
         <v>2.36</v>
@@ -24882,7 +24882,7 @@
         <v>34</v>
       </c>
       <c r="AM96">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AN96">
         <v>8.6</v>
@@ -24894,7 +24894,7 @@
         <v>16.5</v>
       </c>
       <c r="AQ96">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AR96">
         <v>1.03</v>
@@ -24927,7 +24927,7 @@
         <v>1.03</v>
       </c>
       <c r="BB96">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC96">
         <v>12.5</v>
@@ -25025,22 +25025,22 @@
         <v>423</v>
       </c>
       <c r="F97">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="G97">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="H97">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I97">
         <v>6.2</v>
       </c>
       <c r="J97">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K97">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L97">
         <v>1.01</v>
@@ -25049,34 +25049,34 @@
         <v>1.01</v>
       </c>
       <c r="N97">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O97">
         <v>1.18</v>
       </c>
       <c r="P97">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q97">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R97">
         <v>1.64</v>
       </c>
       <c r="S97">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="T97">
         <v>1.63</v>
       </c>
       <c r="U97">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="V97">
         <v>1.19</v>
       </c>
       <c r="W97">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="X97">
         <v>27</v>
@@ -25085,22 +25085,22 @@
         <v>28</v>
       </c>
       <c r="Z97">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA97">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB97">
         <v>13</v>
       </c>
       <c r="AC97">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD97">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE97">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF97">
         <v>15</v>
@@ -25112,13 +25112,13 @@
         <v>18</v>
       </c>
       <c r="AI97">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AJ97">
         <v>20</v>
       </c>
       <c r="AK97">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AL97">
         <v>27</v>
@@ -25130,61 +25130,61 @@
         <v>7.6</v>
       </c>
       <c r="AO97">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AP97">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AQ97">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="AR97">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS97">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="AT97">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AU97">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AV97">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AW97">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="AX97">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AY97">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AZ97">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA97">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BB97">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BC97">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD97">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BE97">
-        <v>1.03</v>
+        <v>5.9</v>
       </c>
       <c r="BF97">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BG97">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BH97">
         <v>1000</v>
@@ -25267,22 +25267,22 @@
         <v>424</v>
       </c>
       <c r="F98">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="G98">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="H98">
         <v>10</v>
       </c>
       <c r="I98">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="J98">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K98">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L98">
         <v>1.01</v>
@@ -25291,34 +25291,34 @@
         <v>1.06</v>
       </c>
       <c r="N98">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O98">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P98">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="Q98">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R98">
         <v>1.37</v>
       </c>
       <c r="S98">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T98">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="U98">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V98">
         <v>1.08</v>
       </c>
       <c r="W98">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="X98">
         <v>19</v>
@@ -25330,7 +25330,7 @@
         <v>120</v>
       </c>
       <c r="AA98">
-        <v>550</v>
+        <v>540</v>
       </c>
       <c r="AB98">
         <v>7.6</v>
@@ -25339,13 +25339,13 @@
         <v>12.5</v>
       </c>
       <c r="AD98">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AE98">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AF98">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AG98">
         <v>11</v>
@@ -25378,13 +25378,13 @@
         <v>14</v>
       </c>
       <c r="AQ98">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR98">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS98">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AT98">
         <v>6.4</v>
@@ -25393,10 +25393,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV98">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AW98">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX98">
         <v>6.6</v>
@@ -25405,10 +25405,10 @@
         <v>9</v>
       </c>
       <c r="AZ98">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA98">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB98">
         <v>9.4</v>
@@ -25417,16 +25417,16 @@
         <v>13.5</v>
       </c>
       <c r="BD98">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE98">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF98">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG98">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BH98">
         <v>1000</v>
@@ -25533,13 +25533,13 @@
         <v>1.01</v>
       </c>
       <c r="N99">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="O99">
         <v>1.16</v>
       </c>
       <c r="P99">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="Q99">
         <v>1.47</v>
@@ -25751,22 +25751,22 @@
         <v>426</v>
       </c>
       <c r="F100">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="G100">
         <v>4.9</v>
       </c>
       <c r="H100">
+        <v>1.77</v>
+      </c>
+      <c r="I100">
         <v>1.78</v>
-      </c>
-      <c r="I100">
-        <v>1.8</v>
       </c>
       <c r="J100">
         <v>4.3</v>
       </c>
       <c r="K100">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L100">
         <v>1.27</v>
@@ -25775,34 +25775,34 @@
         <v>1.03</v>
       </c>
       <c r="N100">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="O100">
         <v>1.19</v>
       </c>
       <c r="P100">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q100">
         <v>1.59</v>
       </c>
       <c r="R100">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S100">
+        <v>2.44</v>
+      </c>
+      <c r="T100">
+        <v>1.62</v>
+      </c>
+      <c r="U100">
         <v>2.42</v>
       </c>
-      <c r="T100">
-        <v>1.61</v>
-      </c>
-      <c r="U100">
-        <v>2.4</v>
-      </c>
       <c r="V100">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="W100">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="X100">
         <v>25</v>
@@ -25817,7 +25817,7 @@
         <v>20</v>
       </c>
       <c r="AB100">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC100">
         <v>10.5</v>
@@ -25829,7 +25829,7 @@
         <v>16.5</v>
       </c>
       <c r="AF100">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AG100">
         <v>20</v>
@@ -25844,16 +25844,16 @@
         <v>120</v>
       </c>
       <c r="AK100">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AL100">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="AM100">
         <v>70</v>
       </c>
       <c r="AN100">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AO100">
         <v>7.6</v>
@@ -25868,7 +25868,7 @@
         <v>11.5</v>
       </c>
       <c r="AS100">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT100">
         <v>20</v>
@@ -25892,19 +25892,19 @@
         <v>14.5</v>
       </c>
       <c r="BA100">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BB100">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC100">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BD100">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BE100">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF100">
         <v>30</v>
@@ -26005,7 +26005,7 @@
         <v>3.2</v>
       </c>
       <c r="J101">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="K101">
         <v>5</v>
@@ -26017,19 +26017,19 @@
         <v>1.01</v>
       </c>
       <c r="N101">
-        <v>2.98</v>
+        <v>4.5</v>
       </c>
       <c r="O101">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P101">
         <v>2.34</v>
       </c>
       <c r="Q101">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="R101">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="S101">
         <v>2.34</v>
@@ -26101,58 +26101,58 @@
         <v>22</v>
       </c>
       <c r="AP101">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ101">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AR101">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AS101">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT101">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AU101">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV101">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AW101">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AX101">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY101">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AZ101">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BA101">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BB101">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BC101">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BD101">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BE101">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF101">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BG101">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BH101">
         <v>1000</v>
@@ -26238,7 +26238,7 @@
         <v>3.5</v>
       </c>
       <c r="G102">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H102">
         <v>2.06</v>
@@ -26247,28 +26247,28 @@
         <v>2.22</v>
       </c>
       <c r="J102">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K102">
         <v>3.9</v>
       </c>
       <c r="L102">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M102">
         <v>1.01</v>
       </c>
       <c r="N102">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="O102">
         <v>1.27</v>
       </c>
       <c r="P102">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q102">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="R102">
         <v>1.4</v>
@@ -26286,7 +26286,7 @@
         <v>1.81</v>
       </c>
       <c r="W102">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X102">
         <v>1000</v>
@@ -26501,28 +26501,28 @@
         <v>1.07</v>
       </c>
       <c r="N103">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="O103">
         <v>1.31</v>
       </c>
       <c r="P103">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q103">
         <v>1.91</v>
       </c>
       <c r="R103">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S103">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T103">
         <v>1.74</v>
       </c>
       <c r="U103">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V103">
         <v>1.81</v>
@@ -26552,7 +26552,7 @@
         <v>12.5</v>
       </c>
       <c r="AE103">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF103">
         <v>30</v>
@@ -26564,7 +26564,7 @@
         <v>18.5</v>
       </c>
       <c r="AI103">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AJ103">
         <v>80</v>
@@ -26579,10 +26579,10 @@
         <v>110</v>
       </c>
       <c r="AN103">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO103">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AP103">
         <v>12</v>
@@ -26594,7 +26594,7 @@
         <v>11.5</v>
       </c>
       <c r="AS103">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AT103">
         <v>12.5</v>
@@ -26609,7 +26609,7 @@
         <v>19.5</v>
       </c>
       <c r="AX103">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AY103">
         <v>13.5</v>
@@ -26618,22 +26618,22 @@
         <v>14.5</v>
       </c>
       <c r="BA103">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB103">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BC103">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BD103">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BE103">
+        <v>7</v>
+      </c>
+      <c r="BF103">
         <v>6.4</v>
-      </c>
-      <c r="BF103">
-        <v>6</v>
       </c>
       <c r="BG103">
         <v>12.5</v>
@@ -26719,7 +26719,7 @@
         <v>430</v>
       </c>
       <c r="F104">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G104">
         <v>6</v>
@@ -26961,22 +26961,22 @@
         <v>431</v>
       </c>
       <c r="F105">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="G105">
         <v>1.92</v>
       </c>
       <c r="H105">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="I105">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="J105">
         <v>3.6</v>
       </c>
       <c r="K105">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L105">
         <v>1.01</v>
@@ -26985,22 +26985,22 @@
         <v>1.07</v>
       </c>
       <c r="N105">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="O105">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="P105">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="Q105">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="R105">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S105">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="T105">
         <v>1.11</v>
@@ -27227,7 +27227,7 @@
         <v>1.01</v>
       </c>
       <c r="N106">
-        <v>2.6</v>
+        <v>2.68</v>
       </c>
       <c r="O106">
         <v>1.31</v>
@@ -27236,7 +27236,7 @@
         <v>1.75</v>
       </c>
       <c r="Q106">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R106">
         <v>1.27</v>
@@ -27475,7 +27475,7 @@
         <v>1.16</v>
       </c>
       <c r="P107">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q107">
         <v>1.48</v>
@@ -27490,7 +27490,7 @@
         <v>1.51</v>
       </c>
       <c r="U107">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="V107">
         <v>1.34</v>
@@ -27687,22 +27687,22 @@
         <v>434</v>
       </c>
       <c r="F108">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G108">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="H108">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I108">
         <v>4.8</v>
       </c>
       <c r="J108">
+        <v>2.84</v>
+      </c>
+      <c r="K108">
         <v>2.92</v>
-      </c>
-      <c r="K108">
-        <v>2.94</v>
       </c>
       <c r="L108">
         <v>1.72</v>
@@ -27711,16 +27711,16 @@
         <v>1.19</v>
       </c>
       <c r="N108">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="O108">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="P108">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="Q108">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R108">
         <v>1.12</v>
@@ -27732,13 +27732,13 @@
         <v>2.7</v>
       </c>
       <c r="U108">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="V108">
         <v>1.26</v>
       </c>
       <c r="W108">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="X108">
         <v>6</v>
@@ -27750,7 +27750,7 @@
         <v>32</v>
       </c>
       <c r="AA108">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB108">
         <v>5.7</v>
@@ -27759,7 +27759,7 @@
         <v>7.4</v>
       </c>
       <c r="AD108">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE108">
         <v>140</v>
@@ -27771,16 +27771,16 @@
         <v>15</v>
       </c>
       <c r="AH108">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AI108">
         <v>260</v>
       </c>
       <c r="AJ108">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK108">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="AL108">
         <v>130</v>
@@ -27789,64 +27789,64 @@
         <v>590</v>
       </c>
       <c r="AN108">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO108">
         <v>340</v>
       </c>
       <c r="AP108">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AQ108">
         <v>8.800000000000001</v>
       </c>
       <c r="AR108">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="AS108">
-        <v>14.5</v>
+        <v>40</v>
       </c>
       <c r="AT108">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AU108">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV108">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AW108">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="AX108">
         <v>10.5</v>
       </c>
       <c r="AY108">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ108">
         <v>32</v>
       </c>
       <c r="BA108">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="BB108">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC108">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="BD108">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="BE108">
-        <v>14.5</v>
+        <v>55</v>
       </c>
       <c r="BF108">
-        <v>12.5</v>
+        <v>34</v>
       </c>
       <c r="BG108">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="BH108">
         <v>1000</v>
@@ -27932,19 +27932,19 @@
         <v>3.2</v>
       </c>
       <c r="G109">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H109">
         <v>2.72</v>
       </c>
       <c r="I109">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J109">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K109">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L109">
         <v>1.62</v>
@@ -27953,13 +27953,13 @@
         <v>1.01</v>
       </c>
       <c r="N109">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O109">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="P109">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Q109">
         <v>3.05</v>
@@ -27968,22 +27968,22 @@
         <v>1.12</v>
       </c>
       <c r="S109">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="T109">
         <v>2.08</v>
       </c>
       <c r="U109">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="V109">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W109">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="X109">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="Y109">
         <v>8.800000000000001</v>
@@ -27992,13 +27992,13 @@
         <v>20</v>
       </c>
       <c r="AA109">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB109">
         <v>10</v>
       </c>
       <c r="AC109">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD109">
         <v>17.5</v>
@@ -28022,7 +28022,7 @@
         <v>90</v>
       </c>
       <c r="AK109">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AL109">
         <v>120</v>
@@ -28037,7 +28037,7 @@
         <v>80</v>
       </c>
       <c r="AP109">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AQ109">
         <v>6.4</v>
@@ -28046,7 +28046,7 @@
         <v>13.5</v>
       </c>
       <c r="AS109">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="AT109">
         <v>7</v>
@@ -28058,7 +28058,7 @@
         <v>12</v>
       </c>
       <c r="AW109">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="AX109">
         <v>17.5</v>
@@ -28067,28 +28067,28 @@
         <v>13.5</v>
       </c>
       <c r="AZ109">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="BA109">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BB109">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="BC109">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BD109">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BE109">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BF109">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BG109">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BH109">
         <v>1000</v>
@@ -28279,52 +28279,52 @@
         <v>90</v>
       </c>
       <c r="AP110">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ110">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="AR110">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS110">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT110">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AU110">
-        <v>7.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV110">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AW110">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX110">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AY110">
-        <v>7.8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ110">
-        <v>15</v>
+        <v>1.03</v>
       </c>
       <c r="BA110">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB110">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BC110">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="BD110">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BE110">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF110">
         <v>7.4</v>
@@ -28425,10 +28425,10 @@
         <v>2.58</v>
       </c>
       <c r="J111">
-        <v>2.58</v>
+        <v>3.2</v>
       </c>
       <c r="K111">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L111">
         <v>1.01</v>
@@ -28440,10 +28440,10 @@
         <v>2.44</v>
       </c>
       <c r="O111">
-        <v>1.42</v>
+        <v>1.02</v>
       </c>
       <c r="P111">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="Q111">
         <v>2.26</v>
@@ -28763,52 +28763,52 @@
         <v>1000</v>
       </c>
       <c r="AP112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE112">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF112">
         <v>1.01</v>
@@ -29193,7 +29193,7 @@
         <v>2.44</v>
       </c>
       <c r="X114">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Y114">
         <v>27</v>
@@ -29217,7 +29217,7 @@
         <v>90</v>
       </c>
       <c r="AF114">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG114">
         <v>11</v>
@@ -29253,10 +29253,10 @@
         <v>18</v>
       </c>
       <c r="AR114">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS114">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT114">
         <v>9</v>
@@ -29268,7 +29268,7 @@
         <v>17</v>
       </c>
       <c r="AW114">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX114">
         <v>9.4</v>
@@ -29280,7 +29280,7 @@
         <v>16.5</v>
       </c>
       <c r="BA114">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB114">
         <v>13.5</v>
@@ -29289,16 +29289,16 @@
         <v>13.5</v>
       </c>
       <c r="BD114">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE114">
+        <v>6.8</v>
+      </c>
+      <c r="BF114">
+        <v>6</v>
+      </c>
+      <c r="BG114">
         <v>6.6</v>
-      </c>
-      <c r="BF114">
-        <v>5.9</v>
-      </c>
-      <c r="BG114">
-        <v>6.4</v>
       </c>
       <c r="BH114">
         <v>1000</v>
@@ -29384,7 +29384,7 @@
         <v>2.34</v>
       </c>
       <c r="G115">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H115">
         <v>3.2</v>
@@ -29626,19 +29626,19 @@
         <v>1.33</v>
       </c>
       <c r="G116">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="H116">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I116">
         <v>870</v>
       </c>
       <c r="J116">
-        <v>3.65</v>
+        <v>4.6</v>
       </c>
       <c r="K116">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="L116">
         <v>1.33</v>
@@ -29647,19 +29647,19 @@
         <v>1.01</v>
       </c>
       <c r="N116">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="O116">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P116">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="Q116">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R116">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S116">
         <v>3</v>
@@ -29671,10 +29671,10 @@
         <v>1.01</v>
       </c>
       <c r="V116">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W116">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="X116">
         <v>1000</v>
@@ -29767,7 +29767,7 @@
         <v>1.01</v>
       </c>
       <c r="BB116">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC116">
         <v>1.01</v>
@@ -29868,7 +29868,7 @@
         <v>1.4</v>
       </c>
       <c r="G117">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="H117">
         <v>5.3</v>
@@ -29889,10 +29889,10 @@
         <v>1.03</v>
       </c>
       <c r="N117">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="O117">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P117">
         <v>2.12</v>
@@ -29916,7 +29916,7 @@
         <v>1.07</v>
       </c>
       <c r="W117">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="X117">
         <v>1000</v>
@@ -29973,52 +29973,52 @@
         <v>1000</v>
       </c>
       <c r="AP117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE117">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF117">
         <v>1.01</v>
@@ -30107,22 +30107,22 @@
         <v>444</v>
       </c>
       <c r="F118">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G118">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="H118">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="I118">
         <v>4.2</v>
       </c>
       <c r="J118">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K118">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L118">
         <v>1.01</v>
@@ -30131,37 +30131,37 @@
         <v>1.07</v>
       </c>
       <c r="N118">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="O118">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P118">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q118">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R118">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S118">
         <v>3.5</v>
       </c>
       <c r="T118">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="U118">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="V118">
         <v>1.31</v>
       </c>
       <c r="W118">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="X118">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y118">
         <v>14.5</v>
@@ -30170,19 +30170,19 @@
         <v>29</v>
       </c>
       <c r="AA118">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AB118">
         <v>9.800000000000001</v>
       </c>
       <c r="AC118">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD118">
         <v>17</v>
       </c>
       <c r="AE118">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF118">
         <v>15.5</v>
@@ -30191,13 +30191,13 @@
         <v>13</v>
       </c>
       <c r="AH118">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI118">
         <v>70</v>
       </c>
       <c r="AJ118">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AK118">
         <v>28</v>
@@ -30209,7 +30209,7 @@
         <v>120</v>
       </c>
       <c r="AN118">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO118">
         <v>60</v>
@@ -30218,25 +30218,25 @@
         <v>10</v>
       </c>
       <c r="AQ118">
-        <v>4.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR118">
-        <v>5.2</v>
+        <v>21</v>
       </c>
       <c r="AS118">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT118">
         <v>7.2</v>
       </c>
       <c r="AU118">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AV118">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AW118">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX118">
         <v>10</v>
@@ -30245,28 +30245,28 @@
         <v>8.4</v>
       </c>
       <c r="AZ118">
-        <v>4.8</v>
+        <v>15.5</v>
       </c>
       <c r="BA118">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BB118">
-        <v>5.3</v>
+        <v>20</v>
       </c>
       <c r="BC118">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD118">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BE118">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF118">
-        <v>4.8</v>
+        <v>13.5</v>
       </c>
       <c r="BG118">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH118">
         <v>1000</v>
@@ -30355,13 +30355,13 @@
         <v>2.08</v>
       </c>
       <c r="H119">
-        <v>1.96</v>
+        <v>3.9</v>
       </c>
       <c r="I119">
         <v>870</v>
       </c>
       <c r="J119">
-        <v>3.7</v>
+        <v>1.96</v>
       </c>
       <c r="K119">
         <v>950</v>
@@ -30391,7 +30391,7 @@
         <v>2.9</v>
       </c>
       <c r="T119">
-        <v>1.66</v>
+        <v>1.01</v>
       </c>
       <c r="U119">
         <v>1.01</v>
@@ -30400,7 +30400,7 @@
         <v>1.29</v>
       </c>
       <c r="W119">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="X119">
         <v>1000</v>
@@ -30457,52 +30457,52 @@
         <v>1000</v>
       </c>
       <c r="AP119">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ119">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR119">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS119">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT119">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU119">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AV119">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW119">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX119">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY119">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ119">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA119">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB119">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC119">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD119">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE119">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF119">
         <v>1.01</v>
@@ -30591,22 +30591,22 @@
         <v>446</v>
       </c>
       <c r="F120">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="G120">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H120">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="I120">
         <v>6.6</v>
       </c>
       <c r="J120">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K120">
-        <v>500</v>
+        <v>6.6</v>
       </c>
       <c r="L120">
         <v>1.01</v>
@@ -30618,7 +30618,7 @@
         <v>2.06</v>
       </c>
       <c r="O120">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="P120">
         <v>2.06</v>
@@ -30642,7 +30642,7 @@
         <v>1.18</v>
       </c>
       <c r="W120">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X120">
         <v>1000</v>
@@ -30699,52 +30699,52 @@
         <v>1000</v>
       </c>
       <c r="AP120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE120">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF120">
         <v>1.01</v>
@@ -30833,16 +30833,16 @@
         <v>447</v>
       </c>
       <c r="F121">
-        <v>4.3</v>
+        <v>2.08</v>
       </c>
       <c r="G121">
-        <v>5.8</v>
+        <v>600</v>
       </c>
       <c r="H121">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="I121">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="J121">
         <v>3.75</v>
@@ -30857,16 +30857,16 @@
         <v>1.01</v>
       </c>
       <c r="N121">
-        <v>1.99</v>
+        <v>1.36</v>
       </c>
       <c r="O121">
         <v>1.26</v>
       </c>
       <c r="P121">
-        <v>1.99</v>
+        <v>1.36</v>
       </c>
       <c r="Q121">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="R121">
         <v>1.36</v>
@@ -30881,10 +30881,10 @@
         <v>1.01</v>
       </c>
       <c r="V121">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="W121">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="X121">
         <v>1000</v>
@@ -30941,52 +30941,52 @@
         <v>1000</v>
       </c>
       <c r="AP121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE121">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF121">
         <v>1.01</v>
@@ -31810,10 +31810,10 @@
         <v>2.74</v>
       </c>
       <c r="I125">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="J125">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K125">
         <v>3.95</v>
@@ -31840,10 +31840,10 @@
         <v>1.4</v>
       </c>
       <c r="S125">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T125">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="U125">
         <v>2.24</v>
@@ -31909,13 +31909,13 @@
         <v>28</v>
       </c>
       <c r="AP125">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ125">
         <v>11</v>
       </c>
       <c r="AR125">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AS125">
         <v>5.9</v>
@@ -31924,7 +31924,7 @@
         <v>10.5</v>
       </c>
       <c r="AU125">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV125">
         <v>11</v>
@@ -31939,7 +31939,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ125">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA125">
         <v>5.8</v>
@@ -32067,7 +32067,7 @@
         <v>1.01</v>
       </c>
       <c r="N126">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O126">
         <v>1.17</v>
@@ -32288,7 +32288,7 @@
         <v>1.73</v>
       </c>
       <c r="G127">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H127">
         <v>5.4</v>
@@ -32315,13 +32315,13 @@
         <v>1.45</v>
       </c>
       <c r="P127">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
       </c>
       <c r="R127">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S127">
         <v>4.5</v>
@@ -32384,7 +32384,7 @@
         <v>55</v>
       </c>
       <c r="AM127">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AN127">
         <v>18</v>
@@ -32408,7 +32408,7 @@
         <v>5.5</v>
       </c>
       <c r="AU127">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV127">
         <v>19.5</v>
@@ -32423,7 +32423,7 @@
         <v>9</v>
       </c>
       <c r="AZ127">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BA127">
         <v>10</v>
@@ -32444,7 +32444,7 @@
         <v>14</v>
       </c>
       <c r="BG127">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH127">
         <v>1000</v>
@@ -32772,7 +32772,7 @@
         <v>3.85</v>
       </c>
       <c r="G129">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="H129">
         <v>2.2</v>
@@ -32793,19 +32793,19 @@
         <v>1.12</v>
       </c>
       <c r="N129">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="O129">
         <v>1.55</v>
       </c>
       <c r="P129">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="Q129">
         <v>2.62</v>
       </c>
       <c r="R129">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S129">
         <v>5.3</v>
@@ -32814,13 +32814,13 @@
         <v>2.16</v>
       </c>
       <c r="U129">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="V129">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W129">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X129">
         <v>9</v>
@@ -32862,7 +32862,7 @@
         <v>120</v>
       </c>
       <c r="AK129">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AL129">
         <v>110</v>
@@ -33011,7 +33011,7 @@
         <v>456</v>
       </c>
       <c r="F130">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="G130">
         <v>110</v>
@@ -33020,13 +33020,13 @@
         <v>2.06</v>
       </c>
       <c r="I130">
+        <v>2.36</v>
+      </c>
+      <c r="J130">
+        <v>1.76</v>
+      </c>
+      <c r="K130">
         <v>110</v>
-      </c>
-      <c r="J130">
-        <v>1.03</v>
-      </c>
-      <c r="K130">
-        <v>5.2</v>
       </c>
       <c r="L130">
         <v>1.01</v>
@@ -33062,7 +33062,7 @@
         <v>1.73</v>
       </c>
       <c r="W130">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X130">
         <v>1000</v>
@@ -33119,52 +33119,52 @@
         <v>1000</v>
       </c>
       <c r="AP130">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AQ130">
-        <v>7</v>
+        <v>1.03</v>
       </c>
       <c r="AR130">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AS130">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AT130">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU130">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV130">
-        <v>8.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW130">
-        <v>18</v>
+        <v>1.03</v>
       </c>
       <c r="AX130">
-        <v>19.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY130">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AZ130">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA130">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BB130">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BC130">
-        <v>36</v>
+        <v>1.03</v>
       </c>
       <c r="BD130">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BE130">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF130">
         <v>1.01</v>
@@ -33256,19 +33256,19 @@
         <v>1.5</v>
       </c>
       <c r="G131">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H131">
-        <v>6.4</v>
+        <v>1.04</v>
       </c>
       <c r="I131">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="J131">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K131">
-        <v>5.8</v>
+        <v>100</v>
       </c>
       <c r="L131">
         <v>1.01</v>
@@ -33283,7 +33283,7 @@
         <v>1.42</v>
       </c>
       <c r="P131">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Q131">
         <v>2.16</v>
@@ -33304,7 +33304,7 @@
         <v>1.1</v>
       </c>
       <c r="W131">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="X131">
         <v>1000</v>
@@ -33495,13 +33495,13 @@
         <v>458</v>
       </c>
       <c r="F132">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="G132">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="H132">
-        <v>1.77</v>
+        <v>1.69</v>
       </c>
       <c r="I132">
         <v>1.93</v>
@@ -33510,7 +33510,7 @@
         <v>3.7</v>
       </c>
       <c r="K132">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="L132">
         <v>1.01</v>
@@ -33845,52 +33845,52 @@
         <v>1000</v>
       </c>
       <c r="AP133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE133">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF133">
         <v>1.01</v>
@@ -34087,52 +34087,52 @@
         <v>1000</v>
       </c>
       <c r="AP134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE134">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF134">
         <v>1.01</v>
@@ -34251,7 +34251,7 @@
         <v>1.11</v>
       </c>
       <c r="P135">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Q135">
         <v>1.41</v>
@@ -34329,52 +34329,52 @@
         <v>1000</v>
       </c>
       <c r="AP135">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AQ135">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR135">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AS135">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="AT135">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="AU135">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AV135">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="AW135">
-        <v>23</v>
+        <v>1.03</v>
       </c>
       <c r="AX135">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY135">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AZ135">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="BA135">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BB135">
-        <v>20</v>
+        <v>1.03</v>
       </c>
       <c r="BC135">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BD135">
-        <v>17</v>
+        <v>1.03</v>
       </c>
       <c r="BE135">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="BF135">
         <v>1.01</v>
@@ -34472,7 +34472,7 @@
         <v>5.5</v>
       </c>
       <c r="I136">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="J136">
         <v>4</v>
@@ -34487,16 +34487,16 @@
         <v>1.06</v>
       </c>
       <c r="N136">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O136">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P136">
         <v>2.06</v>
       </c>
       <c r="Q136">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="R136">
         <v>1.42</v>
@@ -34505,16 +34505,16 @@
         <v>3.05</v>
       </c>
       <c r="T136">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="U136">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V136">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W136">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="X136">
         <v>17.5</v>
@@ -34583,7 +34583,7 @@
         <v>6</v>
       </c>
       <c r="AT136">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU136">
         <v>8.4</v>
@@ -34813,52 +34813,52 @@
         <v>1000</v>
       </c>
       <c r="AP137">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ137">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR137">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS137">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT137">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU137">
-        <v>5.9</v>
+        <v>1.03</v>
       </c>
       <c r="AV137">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW137">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX137">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY137">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ137">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA137">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB137">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC137">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD137">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE137">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF137">
         <v>1.01</v>
@@ -34989,10 +34989,10 @@
         <v>2.66</v>
       </c>
       <c r="T138">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U138">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V138">
         <v>1.1</v>
@@ -35004,7 +35004,7 @@
         <v>1000</v>
       </c>
       <c r="Y138">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z138">
         <v>1000</v>
@@ -35013,34 +35013,34 @@
         <v>1000</v>
       </c>
       <c r="AB138">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC138">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AD138">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AE138">
         <v>1000</v>
       </c>
       <c r="AF138">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG138">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH138">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI138">
         <v>1000</v>
       </c>
       <c r="AJ138">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AK138">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AL138">
         <v>1000</v>
@@ -35055,52 +35055,52 @@
         <v>1000</v>
       </c>
       <c r="AP138">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ138">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AR138">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS138">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT138">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AU138">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV138">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW138">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX138">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AY138">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AZ138">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA138">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB138">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BC138">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BD138">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE138">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF138">
         <v>1.01</v>
@@ -35195,10 +35195,10 @@
         <v>2.02</v>
       </c>
       <c r="H139">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="I139">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J139">
         <v>3.1</v>
@@ -35216,7 +35216,7 @@
         <v>2.36</v>
       </c>
       <c r="O139">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="P139">
         <v>1.52</v>
@@ -35297,52 +35297,52 @@
         <v>1000</v>
       </c>
       <c r="AP139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE139">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF139">
         <v>1.01</v>
@@ -35539,52 +35539,52 @@
         <v>1000</v>
       </c>
       <c r="AP140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE140">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF140">
         <v>1.01</v>
@@ -35781,52 +35781,52 @@
         <v>1000</v>
       </c>
       <c r="AP141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE141">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF141">
         <v>1.01</v>
@@ -35927,7 +35927,7 @@
         <v>4.5</v>
       </c>
       <c r="J142">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K142">
         <v>3.35</v>
@@ -35945,7 +35945,7 @@
         <v>1.58</v>
       </c>
       <c r="P142">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q142">
         <v>2.64</v>
@@ -35960,7 +35960,7 @@
         <v>2.22</v>
       </c>
       <c r="U142">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="V142">
         <v>1.28</v>
@@ -35981,10 +35981,10 @@
         <v>130</v>
       </c>
       <c r="AB142">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC142">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AD142">
         <v>22</v>
@@ -36008,7 +36008,7 @@
         <v>34</v>
       </c>
       <c r="AK142">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL142">
         <v>75</v>
@@ -36029,10 +36029,10 @@
         <v>9.4</v>
       </c>
       <c r="AR142">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AS142">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT142">
         <v>5.9</v>
@@ -36041,10 +36041,10 @@
         <v>6.8</v>
       </c>
       <c r="AV142">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AW142">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX142">
         <v>10.5</v>
@@ -36053,28 +36053,28 @@
         <v>10</v>
       </c>
       <c r="AZ142">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BA142">
+        <v>8.4</v>
+      </c>
+      <c r="BB142">
+        <v>7</v>
+      </c>
+      <c r="BC142">
+        <v>7.2</v>
+      </c>
+      <c r="BD142">
         <v>7.8</v>
       </c>
-      <c r="BB142">
-        <v>6.6</v>
-      </c>
-      <c r="BC142">
-        <v>6.8</v>
-      </c>
-      <c r="BD142">
-        <v>7.4</v>
-      </c>
       <c r="BE142">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF142">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG142">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH142">
         <v>1000</v>
@@ -36163,10 +36163,10 @@
         <v>1.41</v>
       </c>
       <c r="H143">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="I143">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="J143">
         <v>4.6</v>
@@ -36181,7 +36181,7 @@
         <v>1.07</v>
       </c>
       <c r="N143">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O143">
         <v>1.34</v>
@@ -36193,7 +36193,7 @@
         <v>1.99</v>
       </c>
       <c r="R143">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S143">
         <v>3.6</v>
@@ -36217,7 +36217,7 @@
         <v>32</v>
       </c>
       <c r="Z143">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AA143">
         <v>1000</v>
@@ -36232,19 +36232,19 @@
         <v>60</v>
       </c>
       <c r="AE143">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="AF143">
         <v>7.2</v>
       </c>
       <c r="AG143">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH143">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AI143">
-        <v>310</v>
+        <v>290</v>
       </c>
       <c r="AJ143">
         <v>13</v>
@@ -36256,7 +36256,7 @@
         <v>70</v>
       </c>
       <c r="AM143">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="AN143">
         <v>9.4</v>
@@ -36268,13 +36268,13 @@
         <v>12</v>
       </c>
       <c r="AQ143">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR143">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS143">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT143">
         <v>5.6</v>
@@ -36283,10 +36283,10 @@
         <v>10</v>
       </c>
       <c r="AV143">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW143">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX143">
         <v>6</v>
@@ -36298,7 +36298,7 @@
         <v>4.8</v>
       </c>
       <c r="BA143">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB143">
         <v>9.199999999999999</v>
@@ -36307,16 +36307,16 @@
         <v>15</v>
       </c>
       <c r="BD143">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE143">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF143">
         <v>5.9</v>
       </c>
       <c r="BG143">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH143">
         <v>1000</v>
@@ -36402,10 +36402,10 @@
         <v>1.44</v>
       </c>
       <c r="G144">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="H144">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I144">
         <v>8.4</v>
@@ -36420,7 +36420,7 @@
         <v>1.01</v>
       </c>
       <c r="M144">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N144">
         <v>5</v>
@@ -36444,13 +36444,13 @@
         <v>1.87</v>
       </c>
       <c r="U144">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V144">
         <v>1.13</v>
       </c>
       <c r="W144">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="X144">
         <v>24</v>
@@ -36668,7 +36668,7 @@
         <v>2.66</v>
       </c>
       <c r="O145">
-        <v>1.47</v>
+        <v>1.02</v>
       </c>
       <c r="P145">
         <v>1.58</v>
@@ -37125,19 +37125,19 @@
         <v>473</v>
       </c>
       <c r="F147">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="G147">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="H147">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="I147">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="J147">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="K147">
         <v>4.7</v>
@@ -37149,13 +37149,13 @@
         <v>1.01</v>
       </c>
       <c r="N147">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="O147">
         <v>1.14</v>
       </c>
       <c r="P147">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="Q147">
         <v>1.14</v>
@@ -37173,13 +37173,13 @@
         <v>1.01</v>
       </c>
       <c r="V147">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="W147">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X147">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="Y147">
         <v>95</v>
@@ -37188,7 +37188,7 @@
         <v>85</v>
       </c>
       <c r="AA147">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AB147">
         <v>60</v>
@@ -37197,13 +37197,13 @@
         <v>28</v>
       </c>
       <c r="AD147">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE147">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AF147">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG147">
         <v>19.5</v>
@@ -37212,7 +37212,7 @@
         <v>50</v>
       </c>
       <c r="AI147">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="AJ147">
         <v>42</v>
@@ -37221,34 +37221,34 @@
         <v>50</v>
       </c>
       <c r="AL147">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AM147">
-        <v>660</v>
+        <v>590</v>
       </c>
       <c r="AN147">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO147">
-        <v>460</v>
+        <v>410</v>
       </c>
       <c r="AP147">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AQ147">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AR147">
         <v>28</v>
       </c>
       <c r="AS147">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AT147">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AU147">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AV147">
         <v>19.5</v>
@@ -37257,7 +37257,7 @@
         <v>27</v>
       </c>
       <c r="AX147">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AY147">
         <v>12.5</v>
@@ -37266,7 +37266,7 @@
         <v>13</v>
       </c>
       <c r="BA147">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BB147">
         <v>23</v>
@@ -37275,16 +37275,16 @@
         <v>14</v>
       </c>
       <c r="BD147">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="BE147">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BF147">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BG147">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH147">
         <v>1000</v>
@@ -37391,22 +37391,22 @@
         <v>1.01</v>
       </c>
       <c r="N148">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="O148">
         <v>1.33</v>
       </c>
       <c r="P148">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="Q148">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R148">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S148">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="T148">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-02.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-02.xlsx
@@ -1441,7 +1441,7 @@
     <t>Universitario de Deportes</t>
   </si>
   <si>
-    <t>2026-08-01 02:51:55</t>
+    <t>2026-08-01 03:57:15</t>
   </si>
 </sst>
 </file>
@@ -2035,7 +2035,7 @@
         <v>328</v>
       </c>
       <c r="F2">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G2">
         <v>2.54</v>
@@ -2050,7 +2050,7 @@
         <v>3.45</v>
       </c>
       <c r="K2">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L2">
         <v>1.4</v>
@@ -2277,16 +2277,16 @@
         <v>329</v>
       </c>
       <c r="F3">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G3">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H3">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I3">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J3">
         <v>3.2</v>
@@ -2301,7 +2301,7 @@
         <v>1.1</v>
       </c>
       <c r="N3">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="O3">
         <v>1.49</v>
@@ -2310,7 +2310,7 @@
         <v>1.61</v>
       </c>
       <c r="Q3">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R3">
         <v>1.23</v>
@@ -2328,7 +2328,7 @@
         <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -2821,7 +2821,7 @@
         <v>13.5</v>
       </c>
       <c r="Z5">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AA5">
         <v>32</v>
@@ -2833,7 +2833,7 @@
         <v>8.4</v>
       </c>
       <c r="AD5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE5">
         <v>22</v>
@@ -2842,7 +2842,7 @@
         <v>26</v>
       </c>
       <c r="AG5">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH5">
         <v>14.5</v>
@@ -2851,7 +2851,7 @@
         <v>30</v>
       </c>
       <c r="AJ5">
-        <v>60</v>
+        <v>370</v>
       </c>
       <c r="AK5">
         <v>34</v>
@@ -2920,7 +2920,7 @@
         <v>21</v>
       </c>
       <c r="BG5">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BH5">
         <v>4</v>
@@ -3054,7 +3054,7 @@
         <v>1.38</v>
       </c>
       <c r="W6">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="X6">
         <v>27</v>
@@ -3248,10 +3248,10 @@
         <v>1.57</v>
       </c>
       <c r="G7">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="H7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="I7">
         <v>6.2</v>
@@ -3290,7 +3290,7 @@
         <v>1.6</v>
       </c>
       <c r="U7">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="V7">
         <v>1.19</v>
@@ -3338,7 +3338,7 @@
         <v>16.5</v>
       </c>
       <c r="AK7">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AL7">
         <v>24</v>
@@ -3777,13 +3777,13 @@
         <v>2.26</v>
       </c>
       <c r="V9">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="W9">
         <v>1.46</v>
       </c>
       <c r="X9">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Y9">
         <v>11.5</v>
@@ -3816,7 +3816,7 @@
         <v>17.5</v>
       </c>
       <c r="AI9">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AJ9">
         <v>60</v>
@@ -3828,7 +3828,7 @@
         <v>48</v>
       </c>
       <c r="AM9">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AN9">
         <v>50</v>
@@ -3846,7 +3846,7 @@
         <v>14</v>
       </c>
       <c r="AS9">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT9">
         <v>11.5</v>
@@ -3858,7 +3858,7 @@
         <v>10</v>
       </c>
       <c r="AW9">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX9">
         <v>17.5</v>
@@ -3873,7 +3873,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BB9">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC9">
         <v>29</v>
@@ -3882,7 +3882,7 @@
         <v>34</v>
       </c>
       <c r="BE9">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF9">
         <v>21</v>
@@ -4019,7 +4019,7 @@
         <v>1.11</v>
       </c>
       <c r="V10">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W10">
         <v>2.74</v>
@@ -4219,7 +4219,7 @@
         <v>2.82</v>
       </c>
       <c r="H11">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="I11">
         <v>2.8</v>
@@ -4264,7 +4264,7 @@
         <v>1.55</v>
       </c>
       <c r="W11">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X11">
         <v>15</v>
@@ -4458,55 +4458,55 @@
         <v>2.16</v>
       </c>
       <c r="G12">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H12">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I12">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J12">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K12">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L12">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M12">
         <v>1.08</v>
       </c>
       <c r="N12">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="O12">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="P12">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="Q12">
-        <v>2.06</v>
+        <v>1.98</v>
       </c>
       <c r="R12">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="S12">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="T12">
         <v>1.75</v>
       </c>
       <c r="U12">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="V12">
         <v>1.33</v>
       </c>
       <c r="W12">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="X12">
         <v>15.5</v>
@@ -4518,19 +4518,19 @@
         <v>29</v>
       </c>
       <c r="AA12">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB12">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AC12">
         <v>8.199999999999999</v>
       </c>
       <c r="AD12">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF12">
         <v>14.5</v>
@@ -4554,37 +4554,37 @@
         <v>40</v>
       </c>
       <c r="AM12">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN12">
         <v>21</v>
       </c>
       <c r="AO12">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AP12">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ12">
         <v>11.5</v>
       </c>
       <c r="AR12">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="AS12">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT12">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AU12">
         <v>6.6</v>
       </c>
       <c r="AV12">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW12">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="AX12">
         <v>11.5</v>
@@ -4593,22 +4593,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ12">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA12">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB12">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BC12">
         <v>20</v>
       </c>
       <c r="BD12">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE12">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BF12">
         <v>14</v>
@@ -4620,37 +4620,37 @@
         <v>3.35</v>
       </c>
       <c r="BI12">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="BJ12">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK12">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL12">
         <v>1000</v>
       </c>
       <c r="BM12">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN12">
         <v>5.1</v>
       </c>
       <c r="BO12">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP12">
         <v>17</v>
       </c>
       <c r="BQ12">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR12">
         <v>32</v>
       </c>
       <c r="BS12">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BT12">
         <v>7.2</v>
@@ -4659,22 +4659,22 @@
         <v>5.3</v>
       </c>
       <c r="BV12">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BW12">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BX12">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="BY12">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BZ12">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="CA12">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="CB12" t="s">
         <v>475</v>
@@ -4942,7 +4942,7 @@
         <v>1.82</v>
       </c>
       <c r="G14">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H14">
         <v>4.5</v>
@@ -4972,10 +4972,10 @@
         <v>2.26</v>
       </c>
       <c r="Q14">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R14">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S14">
         <v>2.96</v>
@@ -5190,10 +5190,10 @@
         <v>3.15</v>
       </c>
       <c r="I15">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K15">
         <v>4.2</v>
@@ -5229,22 +5229,22 @@
         <v>2.84</v>
       </c>
       <c r="V15">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W15">
         <v>1.78</v>
       </c>
       <c r="X15">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y15">
         <v>21</v>
       </c>
       <c r="Z15">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AA15">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB15">
         <v>16.5</v>
@@ -5253,91 +5253,91 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE15">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AF15">
         <v>19</v>
       </c>
       <c r="AG15">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH15">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AI15">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ15">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="AK15">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AL15">
         <v>28</v>
       </c>
       <c r="AM15">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN15">
         <v>10.5</v>
       </c>
       <c r="AO15">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP15">
         <v>18.5</v>
       </c>
       <c r="AQ15">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR15">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AS15">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="AT15">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU15">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AW15">
         <v>26</v>
       </c>
       <c r="AX15">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AY15">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ15">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA15">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="BB15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC15">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD15">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BE15">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="BF15">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG15">
         <v>16.5</v>
@@ -5423,10 +5423,10 @@
         <v>342</v>
       </c>
       <c r="F16">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="G16">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H16">
         <v>3.05</v>
@@ -5474,7 +5474,7 @@
         <v>1.46</v>
       </c>
       <c r="W16">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X16">
         <v>28</v>
@@ -5528,7 +5528,7 @@
         <v>10.5</v>
       </c>
       <c r="AO16">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AP16">
         <v>25</v>
@@ -5537,7 +5537,7 @@
         <v>18.5</v>
       </c>
       <c r="AR16">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS16">
         <v>46</v>
@@ -5692,7 +5692,7 @@
         <v>6</v>
       </c>
       <c r="O17">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P17">
         <v>2.66</v>
@@ -5770,7 +5770,7 @@
         <v>4.9</v>
       </c>
       <c r="AO17">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP17">
         <v>6.8</v>
@@ -5779,10 +5779,10 @@
         <v>7.4</v>
       </c>
       <c r="AR17">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS17">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT17">
         <v>9.199999999999999</v>
@@ -5907,13 +5907,13 @@
         <v>344</v>
       </c>
       <c r="F18">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G18">
         <v>990</v>
       </c>
       <c r="H18">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I18">
         <v>990</v>
@@ -6179,16 +6179,16 @@
         <v>1.24</v>
       </c>
       <c r="P19">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="Q19">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R19">
         <v>1.37</v>
       </c>
       <c r="S19">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="T19">
         <v>1.11</v>
@@ -6403,7 +6403,7 @@
         <v>990</v>
       </c>
       <c r="J20">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="K20">
         <v>950</v>
@@ -6415,7 +6415,7 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O20">
         <v>1.01</v>
@@ -6633,7 +6633,7 @@
         <v>347</v>
       </c>
       <c r="F21">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G21">
         <v>1.88</v>
@@ -6920,7 +6920,7 @@
         <v>1.96</v>
       </c>
       <c r="U22">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="V22">
         <v>1.12</v>
@@ -6968,7 +6968,7 @@
         <v>970</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AL22">
         <v>1000</v>
@@ -6986,13 +6986,13 @@
         <v>11</v>
       </c>
       <c r="AQ22">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AR22">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AS22">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AT22">
         <v>6</v>
@@ -7001,10 +7001,10 @@
         <v>7.2</v>
       </c>
       <c r="AV22">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AW22">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AX22">
         <v>6.4</v>
@@ -7013,10 +7013,10 @@
         <v>7</v>
       </c>
       <c r="AZ22">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="BA22">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="BB22">
         <v>9</v>
@@ -7025,16 +7025,16 @@
         <v>1.6</v>
       </c>
       <c r="BD22">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="BE22">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="BF22">
         <v>6</v>
       </c>
       <c r="BG22">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -7135,7 +7135,7 @@
         <v>3.95</v>
       </c>
       <c r="L23">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="M23">
         <v>1.06</v>
@@ -7144,16 +7144,16 @@
         <v>4</v>
       </c>
       <c r="O23">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P23">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q23">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R23">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S23">
         <v>3.2</v>
@@ -7162,13 +7162,13 @@
         <v>1.8</v>
       </c>
       <c r="U23">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V23">
         <v>1.3</v>
       </c>
       <c r="W23">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="X23">
         <v>17</v>
@@ -7389,7 +7389,7 @@
         <v>1.5</v>
       </c>
       <c r="P24">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q24">
         <v>2.44</v>
@@ -7849,7 +7849,7 @@
         <v>3.4</v>
       </c>
       <c r="H26">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I26">
         <v>2.72</v>
@@ -7864,7 +7864,7 @@
         <v>1.01</v>
       </c>
       <c r="M26">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N26">
         <v>4.3</v>
@@ -7876,67 +7876,67 @@
         <v>2.14</v>
       </c>
       <c r="Q26">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="R26">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S26">
         <v>2.48</v>
       </c>
       <c r="T26">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="U26">
-        <v>2.14</v>
+        <v>1.11</v>
       </c>
       <c r="V26">
         <v>1.58</v>
       </c>
       <c r="W26">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X26">
         <v>1000</v>
       </c>
       <c r="Y26">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB26">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC26">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF26">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG26">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH26">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ26">
         <v>1000</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AL26">
         <v>1000</v>
@@ -7954,34 +7954,34 @@
         <v>1.03</v>
       </c>
       <c r="AQ26">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AR26">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AS26">
         <v>1.03</v>
       </c>
       <c r="AT26">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU26">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AV26">
-        <v>1.03</v>
+        <v>7.4</v>
       </c>
       <c r="AW26">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AX26">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AY26">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AZ26">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="BA26">
         <v>1.03</v>
@@ -7990,7 +7990,7 @@
         <v>1.03</v>
       </c>
       <c r="BC26">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BD26">
         <v>1.03</v>
@@ -8011,58 +8011,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ26">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK26">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BL26">
         <v>1000</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN26">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BO26">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BR26">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV26">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BX26">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BZ26">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="CA26">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="CB26" t="s">
         <v>475</v>
@@ -9791,7 +9791,7 @@
         <v>990</v>
       </c>
       <c r="J34">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K34">
         <v>500</v>
@@ -10027,10 +10027,10 @@
         <v>4.3</v>
       </c>
       <c r="H35">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="I35">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="J35">
         <v>4.5</v>
@@ -10069,7 +10069,7 @@
         <v>2.66</v>
       </c>
       <c r="V35">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="W35">
         <v>1.3</v>
@@ -10084,7 +10084,7 @@
         <v>16</v>
       </c>
       <c r="AA35">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB35">
         <v>30</v>
@@ -10747,7 +10747,7 @@
         <v>364</v>
       </c>
       <c r="F38">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="G38">
         <v>3.5</v>
@@ -11019,10 +11019,10 @@
         <v>1.17</v>
       </c>
       <c r="P39">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="Q39">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R39">
         <v>1.63</v>
@@ -11231,19 +11231,19 @@
         <v>366</v>
       </c>
       <c r="F40">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G40">
         <v>990</v>
       </c>
       <c r="H40">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I40">
         <v>1000</v>
       </c>
       <c r="J40">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="K40">
         <v>950</v>
@@ -11473,7 +11473,7 @@
         <v>367</v>
       </c>
       <c r="F41">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="G41">
         <v>1.4</v>
@@ -11512,7 +11512,7 @@
         <v>1.62</v>
       </c>
       <c r="S41">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="T41">
         <v>1.87</v>
@@ -11751,7 +11751,7 @@
         <v>1.66</v>
       </c>
       <c r="R42">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="S42">
         <v>2.66</v>
@@ -12441,10 +12441,10 @@
         <v>371</v>
       </c>
       <c r="F45">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G45">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="H45">
         <v>3.2</v>
@@ -12465,16 +12465,16 @@
         <v>1.03</v>
       </c>
       <c r="N45">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O45">
         <v>1.32</v>
       </c>
       <c r="P45">
-        <v>1.81</v>
+        <v>1.94</v>
       </c>
       <c r="Q45">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="R45">
         <v>1.37</v>
@@ -12489,10 +12489,10 @@
         <v>2.04</v>
       </c>
       <c r="V45">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="W45">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="X45">
         <v>36</v>
@@ -13654,7 +13654,7 @@
         <v>2.74</v>
       </c>
       <c r="G50">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="H50">
         <v>3.05</v>
@@ -13663,7 +13663,7 @@
         <v>3.75</v>
       </c>
       <c r="J50">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="K50">
         <v>3.25</v>
@@ -13672,7 +13672,7 @@
         <v>1.6</v>
       </c>
       <c r="M50">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="N50">
         <v>2.1</v>
@@ -13690,7 +13690,7 @@
         <v>1.13</v>
       </c>
       <c r="S50">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="T50">
         <v>1.11</v>
@@ -13702,7 +13702,7 @@
         <v>1.38</v>
       </c>
       <c r="W50">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X50">
         <v>1000</v>
@@ -13893,7 +13893,7 @@
         <v>377</v>
       </c>
       <c r="F51">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G51">
         <v>2.38</v>
@@ -13941,10 +13941,10 @@
         <v>2.16</v>
       </c>
       <c r="V51">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W51">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X51">
         <v>15</v>
@@ -13968,7 +13968,7 @@
         <v>14.5</v>
       </c>
       <c r="AE51">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF51">
         <v>15.5</v>
@@ -13983,7 +13983,7 @@
         <v>48</v>
       </c>
       <c r="AJ51">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK51">
         <v>32</v>
@@ -14025,7 +14025,7 @@
         <v>32</v>
       </c>
       <c r="AX51">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY51">
         <v>10</v>
@@ -14147,7 +14147,7 @@
         <v>870</v>
       </c>
       <c r="J52">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K52">
         <v>500</v>
@@ -14389,7 +14389,7 @@
         <v>990</v>
       </c>
       <c r="J53">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="K53">
         <v>950</v>
@@ -14425,7 +14425,7 @@
         <v>1.11</v>
       </c>
       <c r="V53">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="W53">
         <v>1.02</v>
@@ -14619,13 +14619,13 @@
         <v>380</v>
       </c>
       <c r="F54">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G54">
         <v>990</v>
       </c>
       <c r="H54">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I54">
         <v>990</v>
@@ -14903,7 +14903,7 @@
         <v>2.5</v>
       </c>
       <c r="T55">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="U55">
         <v>1.01</v>
@@ -15106,19 +15106,19 @@
         <v>1.04</v>
       </c>
       <c r="G56">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H56">
         <v>1.04</v>
       </c>
       <c r="I56">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J56">
         <v>1.02</v>
       </c>
       <c r="K56">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L56">
         <v>1.01</v>
@@ -15348,10 +15348,10 @@
         <v>2.12</v>
       </c>
       <c r="G57">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H57">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="I57">
         <v>3.9</v>
@@ -15360,7 +15360,7 @@
         <v>3.45</v>
       </c>
       <c r="K57">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L57">
         <v>1.01</v>
@@ -15396,7 +15396,7 @@
         <v>1.34</v>
       </c>
       <c r="W57">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X57">
         <v>1000</v>
@@ -16254,7 +16254,7 @@
         <v>6.2</v>
       </c>
       <c r="BO60">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BP60">
         <v>14.5</v>
@@ -16322,13 +16322,13 @@
         <v>2.54</v>
       </c>
       <c r="I61">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="J61">
         <v>3.6</v>
       </c>
       <c r="K61">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L61">
         <v>1.01</v>
@@ -16343,7 +16343,7 @@
         <v>1.25</v>
       </c>
       <c r="P61">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q61">
         <v>1.74</v>
@@ -16361,7 +16361,7 @@
         <v>2.42</v>
       </c>
       <c r="V61">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="W61">
         <v>1.51</v>
@@ -17326,7 +17326,7 @@
         <v>1.57</v>
       </c>
       <c r="U65">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="V65">
         <v>1.46</v>
@@ -17625,19 +17625,19 @@
         <v>100</v>
       </c>
       <c r="AN66">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AO66">
         <v>85</v>
       </c>
       <c r="AP66">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AQ66">
         <v>8</v>
       </c>
       <c r="AR66">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AS66">
         <v>10</v>
@@ -17652,7 +17652,7 @@
         <v>19.5</v>
       </c>
       <c r="AW66">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AX66">
         <v>9.6</v>
@@ -17664,7 +17664,7 @@
         <v>17.5</v>
       </c>
       <c r="BA66">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB66">
         <v>12</v>
@@ -17673,16 +17673,16 @@
         <v>13</v>
       </c>
       <c r="BD66">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="BE66">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF66">
         <v>5.3</v>
       </c>
       <c r="BG66">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BH66">
         <v>1000</v>
@@ -18043,7 +18043,7 @@
         <v>1.72</v>
       </c>
       <c r="R68">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S68">
         <v>2.74</v>
@@ -18518,7 +18518,7 @@
         <v>2.36</v>
       </c>
       <c r="O70">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="P70">
         <v>1.51</v>
@@ -18975,7 +18975,7 @@
         <v>398</v>
       </c>
       <c r="F72">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G72">
         <v>4.9</v>
@@ -18990,7 +18990,7 @@
         <v>3.45</v>
       </c>
       <c r="K72">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L72">
         <v>1.01</v>
@@ -19023,10 +19023,10 @@
         <v>1.01</v>
       </c>
       <c r="V72">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="W72">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="X72">
         <v>1000</v>
@@ -19483,16 +19483,16 @@
         <v>1.05</v>
       </c>
       <c r="N74">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O74">
         <v>1.25</v>
       </c>
       <c r="P74">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q74">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R74">
         <v>1.51</v>
@@ -19716,7 +19716,7 @@
         <v>4</v>
       </c>
       <c r="K75">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L75">
         <v>1.01</v>
@@ -20451,28 +20451,28 @@
         <v>1.01</v>
       </c>
       <c r="N78">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="O78">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="P78">
-        <v>2.44</v>
+        <v>2.7</v>
       </c>
       <c r="Q78">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="R78">
         <v>1.62</v>
       </c>
       <c r="S78">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="T78">
-        <v>1.11</v>
+        <v>1.39</v>
       </c>
       <c r="U78">
-        <v>1.11</v>
+        <v>2.46</v>
       </c>
       <c r="V78">
         <v>1.39</v>
@@ -20837,58 +20837,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ79">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK79">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL79">
         <v>1000</v>
       </c>
       <c r="BM79">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN79">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO79">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP79">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BQ79">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BR79">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BS79">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT79">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU79">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BV79">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW79">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BX79">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY79">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ79">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA79">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="CB79" t="s">
         <v>475</v>
@@ -21419,7 +21419,7 @@
         <v>1.01</v>
       </c>
       <c r="N82">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="O82">
         <v>1.18</v>
@@ -21646,7 +21646,7 @@
         <v>6.2</v>
       </c>
       <c r="I83">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J83">
         <v>5.4</v>
@@ -21664,7 +21664,7 @@
         <v>1.1</v>
       </c>
       <c r="O83">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P83">
         <v>3.25</v>
@@ -21676,16 +21676,16 @@
         <v>1.9</v>
       </c>
       <c r="S83">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="T83">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="U83">
         <v>1.11</v>
       </c>
       <c r="V83">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W83">
         <v>2.96</v>
@@ -21703,19 +21703,19 @@
         <v>1000</v>
       </c>
       <c r="AB83">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC83">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AD83">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE83">
         <v>1000</v>
       </c>
       <c r="AF83">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG83">
         <v>1000</v>
@@ -21727,10 +21727,10 @@
         <v>1000</v>
       </c>
       <c r="AJ83">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK83">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL83">
         <v>1000</v>
@@ -21760,16 +21760,16 @@
         <v>1.03</v>
       </c>
       <c r="AU83">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AV83">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AW83">
         <v>1.03</v>
       </c>
       <c r="AX83">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AY83">
         <v>1.03</v>
@@ -21781,10 +21781,10 @@
         <v>1.03</v>
       </c>
       <c r="BB83">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="BC83">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="BD83">
         <v>1.03</v>
@@ -21805,58 +21805,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ83">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK83">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BL83">
         <v>1000</v>
       </c>
       <c r="BM83">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN83">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BO83">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP83">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ83">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BR83">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS83">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BT83">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BU83">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BV83">
         <v>1000</v>
       </c>
       <c r="BW83">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX83">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY83">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ83">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="CA83">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="CB83" t="s">
         <v>475</v>
@@ -22378,7 +22378,7 @@
         <v>3.15</v>
       </c>
       <c r="K86">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L86">
         <v>1.01</v>
@@ -22620,7 +22620,7 @@
         <v>3.5</v>
       </c>
       <c r="K87">
-        <v>8</v>
+        <v>5.4</v>
       </c>
       <c r="L87">
         <v>1.14</v>
@@ -22644,13 +22644,13 @@
         <v>1.31</v>
       </c>
       <c r="S87">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T87">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="U87">
-        <v>1.11</v>
+        <v>1.97</v>
       </c>
       <c r="V87">
         <v>1.43</v>
@@ -22853,16 +22853,16 @@
         <v>3.2</v>
       </c>
       <c r="H88">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I88">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="J88">
         <v>1.1</v>
       </c>
       <c r="K88">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="L88">
         <v>1.16</v>
@@ -22880,7 +22880,7 @@
         <v>1.89</v>
       </c>
       <c r="Q88">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="R88">
         <v>1.31</v>
@@ -23406,7 +23406,7 @@
         <v>14</v>
       </c>
       <c r="AE90">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF90">
         <v>16.5</v>
@@ -23430,7 +23430,7 @@
         <v>38</v>
       </c>
       <c r="AM90">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN90">
         <v>18.5</v>
@@ -23836,7 +23836,7 @@
         <v>1.28</v>
       </c>
       <c r="M92">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N92">
         <v>3.15</v>
@@ -24302,10 +24302,10 @@
         <v>1.27</v>
       </c>
       <c r="G94">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="H94">
-        <v>1.04</v>
+        <v>11</v>
       </c>
       <c r="I94">
         <v>16</v>
@@ -24350,7 +24350,7 @@
         <v>1.06</v>
       </c>
       <c r="W94">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="X94">
         <v>46</v>
@@ -24544,7 +24544,7 @@
         <v>1.73</v>
       </c>
       <c r="G95">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H95">
         <v>5.3</v>
@@ -24583,7 +24583,7 @@
         <v>4</v>
       </c>
       <c r="T95">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U95">
         <v>1.83</v>
@@ -25270,7 +25270,7 @@
         <v>1.36</v>
       </c>
       <c r="G98">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H98">
         <v>10</v>
@@ -25509,7 +25509,7 @@
         <v>425</v>
       </c>
       <c r="F99">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="G99">
         <v>15</v>
@@ -25518,10 +25518,10 @@
         <v>1.28</v>
       </c>
       <c r="I99">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="J99">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="K99">
         <v>7.2</v>
@@ -25533,7 +25533,7 @@
         <v>1.01</v>
       </c>
       <c r="N99">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="O99">
         <v>1.16</v>
@@ -25557,7 +25557,7 @@
         <v>1.9</v>
       </c>
       <c r="V99">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="W99">
         <v>1.07</v>
@@ -25751,7 +25751,7 @@
         <v>426</v>
       </c>
       <c r="F100">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G100">
         <v>4.9</v>
@@ -25784,7 +25784,7 @@
         <v>2.48</v>
       </c>
       <c r="Q100">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R100">
         <v>1.62</v>
@@ -25793,10 +25793,10 @@
         <v>2.44</v>
       </c>
       <c r="T100">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U100">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="V100">
         <v>2.28</v>
@@ -26002,10 +26002,10 @@
         <v>2.74</v>
       </c>
       <c r="I101">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J101">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="K101">
         <v>5</v>
@@ -26035,13 +26035,13 @@
         <v>2.34</v>
       </c>
       <c r="T101">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="U101">
         <v>2.5</v>
       </c>
       <c r="V101">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W101">
         <v>1.63</v>
@@ -26265,13 +26265,13 @@
         <v>1.27</v>
       </c>
       <c r="P102">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="Q102">
         <v>1.86</v>
       </c>
       <c r="R102">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S102">
         <v>3.1</v>
@@ -26286,7 +26286,7 @@
         <v>1.81</v>
       </c>
       <c r="W102">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X102">
         <v>1000</v>
@@ -26522,7 +26522,7 @@
         <v>1.74</v>
       </c>
       <c r="U103">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V103">
         <v>1.81</v>
@@ -26994,7 +26994,7 @@
         <v>1.83</v>
       </c>
       <c r="Q105">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="R105">
         <v>1.3</v>
@@ -27003,7 +27003,7 @@
         <v>3.15</v>
       </c>
       <c r="T105">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="U105">
         <v>1.11</v>
@@ -27490,7 +27490,7 @@
         <v>1.51</v>
       </c>
       <c r="U107">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V107">
         <v>1.34</v>
@@ -27702,7 +27702,7 @@
         <v>2.84</v>
       </c>
       <c r="K108">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="L108">
         <v>1.72</v>
@@ -27711,7 +27711,7 @@
         <v>1.19</v>
       </c>
       <c r="N108">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="O108">
         <v>1.83</v>
@@ -27729,16 +27729,16 @@
         <v>8.6</v>
       </c>
       <c r="T108">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="U108">
         <v>1.52</v>
       </c>
       <c r="V108">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W108">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X108">
         <v>6</v>
@@ -27759,13 +27759,13 @@
         <v>7.4</v>
       </c>
       <c r="AD108">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE108">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF108">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG108">
         <v>15</v>
@@ -27780,19 +27780,19 @@
         <v>36</v>
       </c>
       <c r="AK108">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AL108">
         <v>130</v>
       </c>
       <c r="AM108">
-        <v>590</v>
+        <v>440</v>
       </c>
       <c r="AN108">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO108">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AP108">
         <v>5.5</v>
@@ -27807,7 +27807,7 @@
         <v>40</v>
       </c>
       <c r="AT108">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AU108">
         <v>6.8</v>
@@ -27831,7 +27831,7 @@
         <v>46</v>
       </c>
       <c r="BB108">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BC108">
         <v>24</v>
@@ -27843,7 +27843,7 @@
         <v>55</v>
       </c>
       <c r="BF108">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BG108">
         <v>46</v>
@@ -27932,163 +27932,163 @@
         <v>3.2</v>
       </c>
       <c r="G109">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H109">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="I109">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J109">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="K109">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="L109">
         <v>1.62</v>
       </c>
       <c r="M109">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N109">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="O109">
         <v>1.66</v>
       </c>
       <c r="P109">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Q109">
         <v>3.05</v>
       </c>
       <c r="R109">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="S109">
         <v>6.4</v>
       </c>
       <c r="T109">
-        <v>2.08</v>
+        <v>2.34</v>
       </c>
       <c r="U109">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="V109">
         <v>1.52</v>
       </c>
       <c r="W109">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X109">
         <v>7.4</v>
       </c>
       <c r="Y109">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z109">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AA109">
         <v>55</v>
       </c>
       <c r="AB109">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AC109">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD109">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE109">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AF109">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AG109">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AH109">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AI109">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ109">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AK109">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="AL109">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM109">
         <v>310</v>
       </c>
       <c r="AN109">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO109">
-        <v>80</v>
+        <v>530</v>
       </c>
       <c r="AP109">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ109">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AR109">
         <v>13.5</v>
       </c>
       <c r="AS109">
-        <v>4.9</v>
+        <v>26</v>
       </c>
       <c r="AT109">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU109">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV109">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AW109">
-        <v>4.9</v>
+        <v>26</v>
       </c>
       <c r="AX109">
         <v>17.5</v>
       </c>
       <c r="AY109">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ109">
-        <v>4.6</v>
+        <v>19</v>
       </c>
       <c r="BA109">
-        <v>5.1</v>
+        <v>36</v>
       </c>
       <c r="BB109">
-        <v>5.1</v>
+        <v>30</v>
       </c>
       <c r="BC109">
-        <v>4.9</v>
+        <v>28</v>
       </c>
       <c r="BD109">
-        <v>5.1</v>
+        <v>38</v>
       </c>
       <c r="BE109">
-        <v>5.3</v>
+        <v>100</v>
       </c>
       <c r="BF109">
-        <v>5.1</v>
+        <v>32</v>
       </c>
       <c r="BG109">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="BH109">
         <v>1000</v>
@@ -28180,7 +28180,7 @@
         <v>4.6</v>
       </c>
       <c r="I110">
-        <v>6.6</v>
+        <v>6</v>
       </c>
       <c r="J110">
         <v>4</v>
@@ -28219,7 +28219,7 @@
         <v>2.06</v>
       </c>
       <c r="V110">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W110">
         <v>2.26</v>
@@ -28413,7 +28413,7 @@
         <v>437</v>
       </c>
       <c r="F111">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G111">
         <v>4.4</v>
@@ -28422,10 +28422,10 @@
         <v>2.12</v>
       </c>
       <c r="I111">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="J111">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="K111">
         <v>4.3</v>
@@ -28461,7 +28461,7 @@
         <v>1.11</v>
       </c>
       <c r="V111">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="W111">
         <v>1.29</v>
@@ -28655,7 +28655,7 @@
         <v>438</v>
       </c>
       <c r="F112">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="G112">
         <v>4.8</v>
@@ -28670,7 +28670,7 @@
         <v>3.1</v>
       </c>
       <c r="K112">
-        <v>500</v>
+        <v>6.6</v>
       </c>
       <c r="L112">
         <v>1.01</v>
@@ -29172,7 +29172,7 @@
         <v>2.3</v>
       </c>
       <c r="Q114">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="R114">
         <v>1.5</v>
@@ -29408,7 +29408,7 @@
         <v>3.6</v>
       </c>
       <c r="O115">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P115">
         <v>1.88</v>
@@ -29423,7 +29423,7 @@
         <v>3.4</v>
       </c>
       <c r="T115">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U115">
         <v>2.14</v>
@@ -29659,7 +29659,7 @@
         <v>1.86</v>
       </c>
       <c r="R116">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S116">
         <v>3</v>
@@ -29871,7 +29871,7 @@
         <v>1.69</v>
       </c>
       <c r="H117">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I117">
         <v>15.5</v>
@@ -29880,7 +29880,7 @@
         <v>4.1</v>
       </c>
       <c r="K117">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L117">
         <v>1.01</v>
@@ -29916,7 +29916,7 @@
         <v>1.07</v>
       </c>
       <c r="W117">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="X117">
         <v>1000</v>
@@ -30110,7 +30110,7 @@
         <v>2.06</v>
       </c>
       <c r="G118">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H118">
         <v>3.6</v>
@@ -30122,7 +30122,7 @@
         <v>3.3</v>
       </c>
       <c r="K118">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L118">
         <v>1.01</v>
@@ -30158,7 +30158,7 @@
         <v>1.31</v>
       </c>
       <c r="W118">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="X118">
         <v>15</v>
@@ -30352,7 +30352,7 @@
         <v>1.31</v>
       </c>
       <c r="G119">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H119">
         <v>3.9</v>
@@ -30361,7 +30361,7 @@
         <v>870</v>
       </c>
       <c r="J119">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="K119">
         <v>950</v>
@@ -30373,7 +30373,7 @@
         <v>1.05</v>
       </c>
       <c r="N119">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="O119">
         <v>1.26</v>
@@ -30600,7 +30600,7 @@
         <v>4.4</v>
       </c>
       <c r="I120">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="J120">
         <v>4</v>
@@ -30639,7 +30639,7 @@
         <v>1.01</v>
       </c>
       <c r="V120">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W120">
         <v>2.24</v>
@@ -30857,13 +30857,13 @@
         <v>1.01</v>
       </c>
       <c r="N121">
-        <v>1.36</v>
+        <v>1.98</v>
       </c>
       <c r="O121">
         <v>1.26</v>
       </c>
       <c r="P121">
-        <v>1.36</v>
+        <v>1.98</v>
       </c>
       <c r="Q121">
         <v>1.78</v>
@@ -30884,7 +30884,7 @@
         <v>2.04</v>
       </c>
       <c r="W121">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X121">
         <v>1000</v>
@@ -31574,7 +31574,7 @@
         <v>2.88</v>
       </c>
       <c r="K124">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L124">
         <v>1.38</v>
@@ -31810,10 +31810,10 @@
         <v>2.74</v>
       </c>
       <c r="I125">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J125">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K125">
         <v>3.95</v>
@@ -31828,7 +31828,7 @@
         <v>4.1</v>
       </c>
       <c r="O125">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P125">
         <v>2.02</v>
@@ -31840,16 +31840,16 @@
         <v>1.4</v>
       </c>
       <c r="S125">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="T125">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="U125">
         <v>2.24</v>
       </c>
       <c r="V125">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W125">
         <v>1.57</v>
@@ -31924,7 +31924,7 @@
         <v>10.5</v>
       </c>
       <c r="AU125">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AV125">
         <v>11</v>
@@ -32315,7 +32315,7 @@
         <v>1.45</v>
       </c>
       <c r="P127">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q127">
         <v>2.3</v>
@@ -33014,7 +33014,7 @@
         <v>1.04</v>
       </c>
       <c r="G130">
-        <v>110</v>
+        <v>4.5</v>
       </c>
       <c r="H130">
         <v>2.06</v>
@@ -33023,7 +33023,7 @@
         <v>2.36</v>
       </c>
       <c r="J130">
-        <v>1.76</v>
+        <v>2.82</v>
       </c>
       <c r="K130">
         <v>110</v>
@@ -33062,7 +33062,7 @@
         <v>1.73</v>
       </c>
       <c r="W130">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X130">
         <v>1000</v>
@@ -33256,19 +33256,19 @@
         <v>1.5</v>
       </c>
       <c r="G131">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="H131">
-        <v>1.04</v>
+        <v>6.4</v>
       </c>
       <c r="I131">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="J131">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="K131">
-        <v>100</v>
+        <v>5.8</v>
       </c>
       <c r="L131">
         <v>1.01</v>
@@ -33283,7 +33283,7 @@
         <v>1.42</v>
       </c>
       <c r="P131">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q131">
         <v>2.16</v>
@@ -33304,7 +33304,7 @@
         <v>1.1</v>
       </c>
       <c r="W131">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="X131">
         <v>1000</v>
@@ -33743,7 +33743,7 @@
         <v>3.95</v>
       </c>
       <c r="H133">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I133">
         <v>3.35</v>
@@ -33752,7 +33752,7 @@
         <v>2.6</v>
       </c>
       <c r="K133">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="L133">
         <v>1.01</v>
@@ -33982,19 +33982,19 @@
         <v>1.04</v>
       </c>
       <c r="G134">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H134">
         <v>1.04</v>
       </c>
       <c r="I134">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J134">
         <v>1.04</v>
       </c>
       <c r="K134">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L134">
         <v>1.01</v>
@@ -34236,7 +34236,7 @@
         <v>1.03</v>
       </c>
       <c r="K135">
-        <v>4.9</v>
+        <v>110</v>
       </c>
       <c r="L135">
         <v>1.01</v>
@@ -34254,7 +34254,7 @@
         <v>1.36</v>
       </c>
       <c r="Q135">
-        <v>1.41</v>
+        <v>1.11</v>
       </c>
       <c r="R135">
         <v>1.35</v>
@@ -34269,7 +34269,7 @@
         <v>1.01</v>
       </c>
       <c r="V135">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="W135">
         <v>1.01</v>
@@ -35189,7 +35189,7 @@
         <v>465</v>
       </c>
       <c r="F139">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="G139">
         <v>2.02</v>
@@ -35204,7 +35204,7 @@
         <v>3.1</v>
       </c>
       <c r="K139">
-        <v>3.9</v>
+        <v>5.9</v>
       </c>
       <c r="L139">
         <v>1.01</v>
@@ -35437,16 +35437,16 @@
         <v>1.72</v>
       </c>
       <c r="H140">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="I140">
+        <v>180</v>
+      </c>
+      <c r="J140">
+        <v>1.01</v>
+      </c>
+      <c r="K140">
         <v>110</v>
-      </c>
-      <c r="J140">
-        <v>1.01</v>
-      </c>
-      <c r="K140">
-        <v>1000</v>
       </c>
       <c r="L140">
         <v>1.01</v>
@@ -36083,58 +36083,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ142">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="BK142">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL142">
         <v>1000</v>
       </c>
       <c r="BM142">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN142">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BO142">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BP142">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BQ142">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BR142">
         <v>1000</v>
       </c>
       <c r="BS142">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT142">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU142">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BV142">
         <v>1000</v>
       </c>
       <c r="BW142">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX142">
         <v>1000</v>
       </c>
       <c r="BY142">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ142">
         <v>1000</v>
       </c>
       <c r="CA142">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="CB142" t="s">
         <v>475</v>
@@ -36166,7 +36166,7 @@
         <v>12</v>
       </c>
       <c r="I143">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="J143">
         <v>4.6</v>
@@ -36205,7 +36205,7 @@
         <v>1.57</v>
       </c>
       <c r="V143">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W143">
         <v>3.4</v>
@@ -36641,13 +36641,13 @@
         <v>471</v>
       </c>
       <c r="F145">
-        <v>1.54</v>
+        <v>1.98</v>
       </c>
       <c r="G145">
         <v>3.55</v>
       </c>
       <c r="H145">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="I145">
         <v>2.86</v>
@@ -36671,7 +36671,7 @@
         <v>1.02</v>
       </c>
       <c r="P145">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="Q145">
         <v>2.4</v>
@@ -36749,52 +36749,52 @@
         <v>1000</v>
       </c>
       <c r="AP145">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AQ145">
-        <v>6.4</v>
+        <v>1.03</v>
       </c>
       <c r="AR145">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AS145">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="AT145">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AU145">
-        <v>5.8</v>
+        <v>1.03</v>
       </c>
       <c r="AV145">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW145">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AX145">
-        <v>16</v>
+        <v>1.03</v>
       </c>
       <c r="AY145">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AZ145">
-        <v>16.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA145">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BB145">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BC145">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="BD145">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BE145">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF145">
         <v>1.01</v>
@@ -36991,52 +36991,52 @@
         <v>1000</v>
       </c>
       <c r="AP146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE146">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF146">
         <v>1.01</v>
@@ -37182,7 +37182,7 @@
         <v>130</v>
       </c>
       <c r="Y147">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="Z147">
         <v>85</v>
@@ -37194,13 +37194,13 @@
         <v>60</v>
       </c>
       <c r="AC147">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD147">
         <v>32</v>
       </c>
       <c r="AE147">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AF147">
         <v>40</v>
@@ -37212,7 +37212,7 @@
         <v>50</v>
       </c>
       <c r="AI147">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AJ147">
         <v>42</v>
@@ -37224,13 +37224,13 @@
         <v>130</v>
       </c>
       <c r="AM147">
-        <v>590</v>
+        <v>580</v>
       </c>
       <c r="AN147">
         <v>50</v>
       </c>
       <c r="AO147">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="AP147">
         <v>1.41</v>
@@ -37242,7 +37242,7 @@
         <v>28</v>
       </c>
       <c r="AS147">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AT147">
         <v>1.39</v>
@@ -37257,7 +37257,7 @@
         <v>27</v>
       </c>
       <c r="AX147">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AY147">
         <v>12.5</v>
@@ -37266,7 +37266,7 @@
         <v>13</v>
       </c>
       <c r="BA147">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="BB147">
         <v>23</v>
@@ -37376,10 +37376,10 @@
         <v>2.96</v>
       </c>
       <c r="I148">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="J148">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="K148">
         <v>4.2</v>
@@ -37403,7 +37403,7 @@
         <v>1.99</v>
       </c>
       <c r="R148">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="S148">
         <v>1.99</v>
@@ -37475,52 +37475,52 @@
         <v>1000</v>
       </c>
       <c r="AP148">
-        <v>9.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AQ148">
-        <v>8.800000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="AR148">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS148">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AT148">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AU148">
-        <v>6</v>
+        <v>1.03</v>
       </c>
       <c r="AV148">
-        <v>9.6</v>
+        <v>1.03</v>
       </c>
       <c r="AW148">
-        <v>24</v>
+        <v>1.03</v>
       </c>
       <c r="AX148">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AY148">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ148">
-        <v>14.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA148">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BB148">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BC148">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BD148">
-        <v>29</v>
+        <v>1.03</v>
       </c>
       <c r="BE148">
-        <v>40</v>
+        <v>1.03</v>
       </c>
       <c r="BF148">
         <v>1.01</v>
